--- a/translators/templates/translator_template_v2.0.0.xlsx
+++ b/translators/templates/translator_template_v2.0.0.xlsx
@@ -64,7 +64,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002B5B47"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="9">
@@ -176,7 +187,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -187,6 +198,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -561,96 +575,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="85" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>OpenBDF – Open Building Data Format</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Version 2.0.0 | October 2026 | pre-validation</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>OpenBDF - Open Building Data Format</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OpenBDF is pre-existing intellectual property of the Global Building Data</t>
-        </is>
-      </c>
-    </row>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Version 2.0.0 | October 2026 | pre-release</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Initiative (GBDI) at EPFL. It remains the property of GBDI.</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>OpenBDF is developed by the team of GBDI Global Building Data Initiative at EPFL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>and RISE with technical support from EPFL ENAC-IT4R. This version is shared for</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>This version is shared for expert review ahead of the November 2026 workshops</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>expert review and is not yet validated. Any licence to use it is non-exclusive</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>and is not yet validated. Any licence to use it is non-exclusive and limited to</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>and limited to the purpose for which it was shared. While we welcome feedback</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>the purpose for which it was shared. Material changes to the specification are</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>and proposals to evolve the format, material changes to the specification are to</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>to be agreed with GBDI before they are made, so that the format is not split before it is consolidated.</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>be agreed with GBDI before they are published, so that the format remains</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Author: Dr Eng. Nicole Di Santo, Technical Lead, GBDI, LMC, EPFL, Lausanne.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>coherent and adjustments can be consolidated ahead of releases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Parser and code implementation: ENAC-IT4R, EPFL, Lausanne</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Code repository: https://github.com/EPFL-ENAC/lmc-openbdf/</t>
+          <t>Authors: Nicole Di Santo¹, Martin Röck²</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Contributors: Karen Scrivener¹, Vanderley John³, Zuhaib Batra¹</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1. GBDI Global Building Data Initiative, EPFL LMC, Lausanne, Switzerland</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2. RISE Institute for Regenerative Spatial Systems Science, Vienna, Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3. University of São Paulo, São Paulo, Brazil</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Contacts:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>nicole.disanto@epfl.ch</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>martin.roeck@riselabs.at</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Parser and code implementation with support of ENAC-IT4R, EPFL, Lausanne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GitHub repository:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/EPFL-ENAC/lmc-openbdf/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -709,8 +792,6 @@
           <t>Afghanistan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -723,8 +804,6 @@
           <t>Albania</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -737,8 +816,6 @@
           <t>Algeria</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -751,8 +828,6 @@
           <t>American Samoa</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -765,8 +840,6 @@
           <t>Andorra</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -779,8 +852,6 @@
           <t>Angola</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -793,8 +864,6 @@
           <t>Anguilla</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -807,8 +876,6 @@
           <t>Antarctica</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -821,8 +888,6 @@
           <t>Antigua and Barbuda</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -835,8 +900,6 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -849,8 +912,6 @@
           <t>Armenia</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -863,8 +924,6 @@
           <t>Aruba</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -877,8 +936,6 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -891,8 +948,6 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -905,8 +960,6 @@
           <t>Azerbaijan</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -919,8 +972,6 @@
           <t>Bahamas (the)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -933,8 +984,6 @@
           <t>Bahrain</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -947,8 +996,6 @@
           <t>Bangladesh</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -961,8 +1008,6 @@
           <t>Barbados</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -975,8 +1020,6 @@
           <t>Belarus</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -989,8 +1032,6 @@
           <t>Belgium</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -1003,8 +1044,6 @@
           <t>Belize</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -1017,8 +1056,6 @@
           <t>Benin</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -1031,8 +1068,6 @@
           <t>Bermuda</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
@@ -1045,8 +1080,6 @@
           <t>Bhutan</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
@@ -1059,8 +1092,6 @@
           <t>Bolivia (Plurinational State of)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
@@ -1073,8 +1104,6 @@
           <t>Bonaire, Sint Eustatius and Saba</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
@@ -1087,8 +1116,6 @@
           <t>Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
@@ -1101,8 +1128,6 @@
           <t>Botswana</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
@@ -1115,8 +1140,6 @@
           <t>Bouvet Island</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
@@ -1129,8 +1152,6 @@
           <t>Brazil</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
@@ -1143,8 +1164,6 @@
           <t>British Indian Ocean Territory (the)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
@@ -1157,8 +1176,6 @@
           <t>Brunei Darussalam</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
@@ -1171,8 +1188,6 @@
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="2" t="inlineStr">
@@ -1185,8 +1200,6 @@
           <t>Burkina Faso</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="2" t="inlineStr">
@@ -1199,8 +1212,6 @@
           <t>Burundi</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="2" t="inlineStr">
@@ -1213,8 +1224,6 @@
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="2" t="inlineStr">
@@ -1227,8 +1236,6 @@
           <t>Cambodia</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="2" t="inlineStr">
@@ -1241,8 +1248,6 @@
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="2" t="inlineStr">
@@ -1255,8 +1260,6 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="2" t="inlineStr">
@@ -1269,8 +1272,6 @@
           <t>Cayman Islands (the)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="2" t="inlineStr">
@@ -1283,8 +1284,6 @@
           <t>Central African Republic (the)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="2" t="inlineStr">
@@ -1297,8 +1296,6 @@
           <t>Chad</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="2" t="inlineStr">
@@ -1311,8 +1308,6 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="2" t="inlineStr">
@@ -1325,8 +1320,6 @@
           <t>China</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="2" t="inlineStr">
@@ -1339,8 +1332,6 @@
           <t>Christmas Island</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="2" t="inlineStr">
@@ -1353,8 +1344,6 @@
           <t>Cocos (Keeling) Islands (the)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="2" t="inlineStr">
@@ -1367,8 +1356,6 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="2" t="inlineStr">
@@ -1381,8 +1368,6 @@
           <t>Comoros (the)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="2" t="inlineStr">
@@ -1395,8 +1380,6 @@
           <t>Congo (the Democratic Republic of the)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="2" t="inlineStr">
@@ -1409,8 +1392,6 @@
           <t>Congo (the)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="2" t="inlineStr">
@@ -1423,8 +1404,6 @@
           <t>Cook Islands (the)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="2" t="inlineStr">
@@ -1437,8 +1416,6 @@
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="2" t="inlineStr">
@@ -1451,8 +1428,6 @@
           <t>Croatia</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="2" t="inlineStr">
@@ -1465,8 +1440,6 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="2" t="inlineStr">
@@ -1479,8 +1452,6 @@
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="2" t="inlineStr">
@@ -1493,8 +1464,6 @@
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="2" t="inlineStr">
@@ -1507,8 +1476,6 @@
           <t>Czechia</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="2" t="inlineStr">
@@ -1521,8 +1488,6 @@
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="2" t="inlineStr">
@@ -1535,8 +1500,6 @@
           <t>Denmark</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="2" t="inlineStr">
@@ -1549,8 +1512,6 @@
           <t>Djibouti</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="2" t="inlineStr">
@@ -1563,8 +1524,6 @@
           <t>Dominica</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="2" t="inlineStr">
@@ -1577,8 +1536,6 @@
           <t>Dominican Republic (the)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="2" t="inlineStr">
@@ -1591,8 +1548,6 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="2" t="inlineStr">
@@ -1605,8 +1560,6 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="2" t="inlineStr">
@@ -1619,8 +1572,6 @@
           <t>El Salvador</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="2" t="inlineStr">
@@ -1633,8 +1584,6 @@
           <t>Equatorial Guinea</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="2" t="inlineStr">
@@ -1647,8 +1596,6 @@
           <t>Eritrea</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="2" t="inlineStr">
@@ -1661,8 +1608,6 @@
           <t>Estonia</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="2" t="inlineStr">
@@ -1675,8 +1620,6 @@
           <t>Eswatini</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="2" t="inlineStr">
@@ -1689,8 +1632,6 @@
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="2" t="inlineStr">
@@ -1703,8 +1644,6 @@
           <t>Falkland Islands (the) [Malvinas]</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="2" t="inlineStr">
@@ -1717,8 +1656,6 @@
           <t>Faroe Islands (the)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="2" t="inlineStr">
@@ -1731,8 +1668,6 @@
           <t>Fiji</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="2" t="inlineStr">
@@ -1745,8 +1680,6 @@
           <t>Finland</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="2" t="inlineStr">
@@ -1759,8 +1692,6 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="2" t="inlineStr">
@@ -1773,8 +1704,6 @@
           <t>French Guiana</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="2" t="inlineStr">
@@ -1787,8 +1716,6 @@
           <t>French Polynesia</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="2" t="inlineStr">
@@ -1801,8 +1728,6 @@
           <t>French Southern Territories (the)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="2" t="inlineStr">
@@ -1815,8 +1740,6 @@
           <t>Gabon</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="2" t="inlineStr">
@@ -1829,8 +1752,6 @@
           <t>Gambia (the)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="2" t="inlineStr">
@@ -1843,8 +1764,6 @@
           <t>Georgia</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="2" t="inlineStr">
@@ -1857,8 +1776,6 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="2" t="inlineStr">
@@ -1871,8 +1788,6 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="2" t="inlineStr">
@@ -1885,8 +1800,6 @@
           <t>Gibraltar</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="2" t="inlineStr">
@@ -1899,8 +1812,6 @@
           <t>Greece</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="2" t="inlineStr">
@@ -1913,8 +1824,6 @@
           <t>Greenland</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="2" t="inlineStr">
@@ -1927,8 +1836,6 @@
           <t>Grenada</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="2" t="inlineStr">
@@ -1941,8 +1848,6 @@
           <t>Guadeloupe</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="2" t="inlineStr">
@@ -1955,8 +1860,6 @@
           <t>Guam</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="2" t="inlineStr">
@@ -1969,8 +1872,6 @@
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="2" t="inlineStr">
@@ -1983,8 +1884,6 @@
           <t>Guernsey</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="2" t="inlineStr">
@@ -1997,8 +1896,6 @@
           <t>Guinea</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="2" t="inlineStr">
@@ -2011,8 +1908,6 @@
           <t>Guinea-Bissau</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="2" t="inlineStr">
@@ -2025,8 +1920,6 @@
           <t>Guyana</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="2" t="inlineStr">
@@ -2039,8 +1932,6 @@
           <t>Haiti</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="2" t="inlineStr">
@@ -2053,8 +1944,6 @@
           <t>Heard Island and McDonald Islands</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="2" t="inlineStr">
@@ -2067,8 +1956,6 @@
           <t>Holy See (the)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="2" t="inlineStr">
@@ -2081,8 +1968,6 @@
           <t>Honduras</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="2" t="inlineStr">
@@ -2095,8 +1980,6 @@
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="2" t="inlineStr">
@@ -2109,8 +1992,6 @@
           <t>Hungary</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="2" t="inlineStr">
@@ -2123,8 +2004,6 @@
           <t>Iceland</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="2" t="inlineStr">
@@ -2137,8 +2016,6 @@
           <t>India</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="2" t="inlineStr">
@@ -2151,8 +2028,6 @@
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="2" t="inlineStr">
@@ -2165,8 +2040,6 @@
           <t>Iran (Islamic Republic of)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="2" t="inlineStr">
@@ -2179,8 +2052,6 @@
           <t>Iraq</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="2" t="inlineStr">
@@ -2193,8 +2064,6 @@
           <t>Ireland</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="2" t="inlineStr">
@@ -2207,8 +2076,6 @@
           <t>Isle of Man</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="2" t="inlineStr">
@@ -2221,8 +2088,6 @@
           <t>Israel</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="2" t="inlineStr">
@@ -2235,8 +2100,6 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="2" t="inlineStr">
@@ -2249,8 +2112,6 @@
           <t>Jamaica</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" s="2" t="inlineStr">
@@ -2263,8 +2124,6 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" s="2" t="inlineStr">
@@ -2277,8 +2136,6 @@
           <t>Jersey</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="B115" s="2" t="inlineStr">
@@ -2291,8 +2148,6 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="B116" s="2" t="inlineStr">
@@ -2305,8 +2160,6 @@
           <t>Kazakhstan</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="B117" s="2" t="inlineStr">
@@ -2319,8 +2172,6 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="B118" s="2" t="inlineStr">
@@ -2333,8 +2184,6 @@
           <t>Kiribati</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="B119" s="2" t="inlineStr">
@@ -2347,8 +2196,6 @@
           <t>Korea (the Democratic People's Republic of)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="B120" s="2" t="inlineStr">
@@ -2361,8 +2208,6 @@
           <t>Korea (the Republic of)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="B121" s="2" t="inlineStr">
@@ -2375,8 +2220,6 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="B122" s="2" t="inlineStr">
@@ -2389,8 +2232,6 @@
           <t>Kyrgyzstan</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="B123" s="2" t="inlineStr">
@@ -2403,8 +2244,6 @@
           <t>Lao People's Democratic Republic (the)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="B124" s="2" t="inlineStr">
@@ -2417,8 +2256,6 @@
           <t>Latvia</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="B125" s="2" t="inlineStr">
@@ -2431,8 +2268,6 @@
           <t>Lebanon</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="B126" s="2" t="inlineStr">
@@ -2445,8 +2280,6 @@
           <t>Lesotho</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="B127" s="2" t="inlineStr">
@@ -2459,8 +2292,6 @@
           <t>Liberia</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="B128" s="2" t="inlineStr">
@@ -2473,8 +2304,6 @@
           <t>Libya</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="B129" s="2" t="inlineStr">
@@ -2487,8 +2316,6 @@
           <t>Liechtenstein</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="B130" s="2" t="inlineStr">
@@ -2501,8 +2328,6 @@
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="B131" s="2" t="inlineStr">
@@ -2515,8 +2340,6 @@
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="B132" s="2" t="inlineStr">
@@ -2529,8 +2352,6 @@
           <t>Macao</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="B133" s="2" t="inlineStr">
@@ -2543,8 +2364,6 @@
           <t>Madagascar</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="B134" s="2" t="inlineStr">
@@ -2557,8 +2376,6 @@
           <t>Malawi</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="B135" s="2" t="inlineStr">
@@ -2571,8 +2388,6 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="B136" s="2" t="inlineStr">
@@ -2585,8 +2400,6 @@
           <t>Maldives</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="B137" s="2" t="inlineStr">
@@ -2599,8 +2412,6 @@
           <t>Mali</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="B138" s="2" t="inlineStr">
@@ -2613,8 +2424,6 @@
           <t>Malta</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="B139" s="2" t="inlineStr">
@@ -2627,8 +2436,6 @@
           <t>Marshall Islands (the)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="B140" s="2" t="inlineStr">
@@ -2641,8 +2448,6 @@
           <t>Martinique</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="B141" s="2" t="inlineStr">
@@ -2655,8 +2460,6 @@
           <t>Mauritania</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="B142" s="2" t="inlineStr">
@@ -2669,8 +2472,6 @@
           <t>Mauritius</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="B143" s="2" t="inlineStr">
@@ -2683,8 +2484,6 @@
           <t>Mayotte</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="B144" s="2" t="inlineStr">
@@ -2697,8 +2496,6 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="B145" s="2" t="inlineStr">
@@ -2711,8 +2508,6 @@
           <t>Micronesia (Federated States of)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="B146" s="2" t="inlineStr">
@@ -2725,8 +2520,6 @@
           <t>Moldova (the Republic of)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="B147" s="2" t="inlineStr">
@@ -2739,8 +2532,6 @@
           <t>Monaco</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="B148" s="2" t="inlineStr">
@@ -2753,8 +2544,6 @@
           <t>Mongolia</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="B149" s="2" t="inlineStr">
@@ -2767,8 +2556,6 @@
           <t>Montenegro</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="B150" s="2" t="inlineStr">
@@ -2781,8 +2568,6 @@
           <t>Montserrat</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="B151" s="2" t="inlineStr">
@@ -2795,8 +2580,6 @@
           <t>Morocco</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="B152" s="2" t="inlineStr">
@@ -2809,8 +2592,6 @@
           <t>Mozambique</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="B153" s="2" t="inlineStr">
@@ -2823,8 +2604,6 @@
           <t>Myanmar</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="B154" s="2" t="inlineStr">
@@ -2837,8 +2616,6 @@
           <t>Namibia</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="B155" s="2" t="inlineStr">
@@ -2851,8 +2628,6 @@
           <t>Nauru</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="B156" s="2" t="inlineStr">
@@ -2865,8 +2640,6 @@
           <t>Nepal</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="B157" s="2" t="inlineStr">
@@ -2879,8 +2652,6 @@
           <t>Netherlands (the)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="B158" s="2" t="inlineStr">
@@ -2893,8 +2664,6 @@
           <t>New Caledonia</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="B159" s="2" t="inlineStr">
@@ -2907,8 +2676,6 @@
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="B160" s="2" t="inlineStr">
@@ -2921,8 +2688,6 @@
           <t>Nicaragua</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="B161" s="2" t="inlineStr">
@@ -2935,8 +2700,6 @@
           <t>Niger (the)</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="B162" s="2" t="inlineStr">
@@ -2949,8 +2712,6 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="B163" s="2" t="inlineStr">
@@ -2963,8 +2724,6 @@
           <t>Niue</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="B164" s="2" t="inlineStr">
@@ -2977,8 +2736,6 @@
           <t>Norfolk Island</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="B165" s="2" t="inlineStr">
@@ -2991,8 +2748,6 @@
           <t>Northern Mariana Islands (the)</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="B166" s="2" t="inlineStr">
@@ -3005,8 +2760,6 @@
           <t>Norway</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="B167" s="2" t="inlineStr">
@@ -3019,8 +2772,6 @@
           <t>Oman</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="B168" s="2" t="inlineStr">
@@ -3033,8 +2784,6 @@
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="B169" s="2" t="inlineStr">
@@ -3047,8 +2796,6 @@
           <t>Palau</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="B170" s="2" t="inlineStr">
@@ -3061,8 +2808,6 @@
           <t>Palestine, State of</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="B171" s="2" t="inlineStr">
@@ -3075,8 +2820,6 @@
           <t>Panama</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="B172" s="2" t="inlineStr">
@@ -3089,8 +2832,6 @@
           <t>Papua New Guinea</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="B173" s="2" t="inlineStr">
@@ -3103,8 +2844,6 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="B174" s="2" t="inlineStr">
@@ -3117,8 +2856,6 @@
           <t>Peru</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="B175" s="2" t="inlineStr">
@@ -3131,8 +2868,6 @@
           <t>Philippines (the)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="B176" s="2" t="inlineStr">
@@ -3145,8 +2880,6 @@
           <t>Pitcairn</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="B177" s="2" t="inlineStr">
@@ -3159,8 +2892,6 @@
           <t>Poland</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="B178" s="2" t="inlineStr">
@@ -3173,8 +2904,6 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="B179" s="2" t="inlineStr">
@@ -3187,8 +2916,6 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="B180" s="2" t="inlineStr">
@@ -3201,8 +2928,6 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="B181" s="2" t="inlineStr">
@@ -3215,8 +2940,6 @@
           <t>Republic of North Macedonia</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="B182" s="2" t="inlineStr">
@@ -3229,8 +2952,6 @@
           <t>Romania</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="B183" s="2" t="inlineStr">
@@ -3243,8 +2964,6 @@
           <t>Russian Federation (the)</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="B184" s="2" t="inlineStr">
@@ -3257,8 +2976,6 @@
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="B185" s="2" t="inlineStr">
@@ -3271,8 +2988,6 @@
           <t>Réunion</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="B186" s="2" t="inlineStr">
@@ -3285,8 +3000,6 @@
           <t>Saint Barthélemy</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="B187" s="2" t="inlineStr">
@@ -3299,8 +3012,6 @@
           <t>Saint Helena, Ascension and Tristan da Cunha</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="B188" s="2" t="inlineStr">
@@ -3313,8 +3024,6 @@
           <t>Saint Kitts and Nevis</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="B189" s="2" t="inlineStr">
@@ -3327,8 +3036,6 @@
           <t>Saint Lucia</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="B190" s="2" t="inlineStr">
@@ -3341,8 +3048,6 @@
           <t>Saint Martin (French part)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="B191" s="2" t="inlineStr">
@@ -3355,8 +3060,6 @@
           <t>Saint Pierre and Miquelon</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="B192" s="2" t="inlineStr">
@@ -3369,8 +3072,6 @@
           <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="B193" s="2" t="inlineStr">
@@ -3383,8 +3084,6 @@
           <t>Samoa</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="B194" s="2" t="inlineStr">
@@ -3397,8 +3096,6 @@
           <t>San Marino</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="B195" s="2" t="inlineStr">
@@ -3411,8 +3108,6 @@
           <t>Sao Tome and Principe</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="B196" s="2" t="inlineStr">
@@ -3425,8 +3120,6 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="B197" s="2" t="inlineStr">
@@ -3439,8 +3132,6 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="B198" s="2" t="inlineStr">
@@ -3453,8 +3144,6 @@
           <t>Serbia</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="B199" s="2" t="inlineStr">
@@ -3467,8 +3156,6 @@
           <t>Seychelles</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="B200" s="2" t="inlineStr">
@@ -3481,8 +3168,6 @@
           <t>Sierra Leone</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="B201" s="2" t="inlineStr">
@@ -3495,8 +3180,6 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="B202" s="2" t="inlineStr">
@@ -3509,8 +3192,6 @@
           <t>Sint Maarten (Dutch part)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="B203" s="2" t="inlineStr">
@@ -3523,8 +3204,6 @@
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="B204" s="2" t="inlineStr">
@@ -3537,8 +3216,6 @@
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="B205" s="2" t="inlineStr">
@@ -3551,8 +3228,6 @@
           <t>Solomon Islands</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="B206" s="2" t="inlineStr">
@@ -3565,8 +3240,6 @@
           <t>Somalia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="B207" s="2" t="inlineStr">
@@ -3579,8 +3252,6 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="B208" s="2" t="inlineStr">
@@ -3593,8 +3264,6 @@
           <t>South Georgia and the South Sandwich Islands</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="B209" s="2" t="inlineStr">
@@ -3607,8 +3276,6 @@
           <t>South Sudan</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="B210" s="2" t="inlineStr">
@@ -3621,8 +3288,6 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="B211" s="2" t="inlineStr">
@@ -3635,8 +3300,6 @@
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="B212" s="2" t="inlineStr">
@@ -3649,8 +3312,6 @@
           <t>Sudan (the)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="B213" s="2" t="inlineStr">
@@ -3663,8 +3324,6 @@
           <t>Suriname</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="B214" s="2" t="inlineStr">
@@ -3677,8 +3336,6 @@
           <t>Svalbard and Jan Mayen</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="B215" s="2" t="inlineStr">
@@ -3691,8 +3348,6 @@
           <t>Sweden</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="B216" s="2" t="inlineStr">
@@ -3705,8 +3360,6 @@
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="B217" s="2" t="inlineStr">
@@ -3719,8 +3372,6 @@
           <t>Syrian Arab Republic</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="B218" s="2" t="inlineStr">
@@ -3733,8 +3384,6 @@
           <t>Taiwan (Province of China)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="B219" s="2" t="inlineStr">
@@ -3747,8 +3396,6 @@
           <t>Tajikistan</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="B220" s="2" t="inlineStr">
@@ -3761,8 +3408,6 @@
           <t>Tanzania, United Republic of</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="B221" s="2" t="inlineStr">
@@ -3775,8 +3420,6 @@
           <t>Thailand</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="B222" s="2" t="inlineStr">
@@ -3789,8 +3432,6 @@
           <t>Timor-Leste</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="B223" s="2" t="inlineStr">
@@ -3803,8 +3444,6 @@
           <t>Togo</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="B224" s="2" t="inlineStr">
@@ -3817,8 +3456,6 @@
           <t>Tokelau</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="B225" s="2" t="inlineStr">
@@ -3831,8 +3468,6 @@
           <t>Tonga</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="B226" s="2" t="inlineStr">
@@ -3845,8 +3480,6 @@
           <t>Trinidad and Tobago</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="B227" s="2" t="inlineStr">
@@ -3859,8 +3492,6 @@
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="B228" s="2" t="inlineStr">
@@ -3873,8 +3504,6 @@
           <t>Turkey</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="B229" s="2" t="inlineStr">
@@ -3887,8 +3516,6 @@
           <t>Turkmenistan</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="B230" s="2" t="inlineStr">
@@ -3901,8 +3528,6 @@
           <t>Turks and Caicos Islands (the)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="B231" s="2" t="inlineStr">
@@ -3915,8 +3540,6 @@
           <t>Tuvalu</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="B232" s="2" t="inlineStr">
@@ -3929,8 +3552,6 @@
           <t>Uganda</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="B233" s="2" t="inlineStr">
@@ -3943,8 +3564,6 @@
           <t>Ukraine</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="B234" s="2" t="inlineStr">
@@ -3957,8 +3576,6 @@
           <t>United Arab Emirates (the)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="B235" s="2" t="inlineStr">
@@ -3971,8 +3588,6 @@
           <t>United Kingdom of Great Britain and Northern Ireland (the)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="B236" s="2" t="inlineStr">
@@ -3985,8 +3600,6 @@
           <t>United States Minor Outlying Islands (the)</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="B237" s="2" t="inlineStr">
@@ -3999,8 +3612,6 @@
           <t>United States of America (the)</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="B238" s="2" t="inlineStr">
@@ -4013,8 +3624,6 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="B239" s="2" t="inlineStr">
@@ -4027,8 +3636,6 @@
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="B240" s="2" t="inlineStr">
@@ -4041,8 +3648,6 @@
           <t>Vanuatu</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="B241" s="2" t="inlineStr">
@@ -4055,8 +3660,6 @@
           <t>Venezuela (Bolivarian Republic of)</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="B242" s="2" t="inlineStr">
@@ -4069,8 +3672,6 @@
           <t>Viet Nam</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="B243" s="2" t="inlineStr">
@@ -4083,8 +3684,6 @@
           <t>Virgin Islands (British)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="B244" s="2" t="inlineStr">
@@ -4097,8 +3696,6 @@
           <t>Virgin Islands (U.S.)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="B245" s="2" t="inlineStr">
@@ -4111,8 +3708,6 @@
           <t>Wallis and Futuna</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="B246" s="2" t="inlineStr">
@@ -4125,8 +3720,6 @@
           <t>Western Sahara</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="B247" s="2" t="inlineStr">
@@ -4139,8 +3732,6 @@
           <t>Yemen</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="B248" s="2" t="inlineStr">
@@ -4153,8 +3744,6 @@
           <t>Zambia</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="B249" s="2" t="inlineStr">
@@ -4167,8 +3756,6 @@
           <t>Zimbabwe</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="B250" s="2" t="inlineStr">
@@ -4181,8 +3768,6 @@
           <t>Åland Islands</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4243,8 +3828,6 @@
           <t>RIBA_UK_0_StrategicDefinition</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -4257,8 +3840,6 @@
           <t>RIBA_UK_1_PreparationAndBriefing</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -4271,8 +3852,6 @@
           <t>RIBA_UK_2_ConceptDesign</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -4285,8 +3864,6 @@
           <t>RIBA_UK_3_SpatialCoordination</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -4299,8 +3876,6 @@
           <t>RIBA_UK_4_TechnicalDesign</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -4313,8 +3888,6 @@
           <t>RIBA_UK_5_ManufacturingAndConstruction</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -4327,8 +3900,6 @@
           <t>RIBA_UK_6_Handover</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -4341,8 +3912,6 @@
           <t>RIBA_UK_7_Use</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -4355,8 +3924,6 @@
           <t>HOAI_DE_LP1_Grundlagenermittlung</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -4369,8 +3936,6 @@
           <t>HOAI_DE_LP2_Vorplanung</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -4383,8 +3948,6 @@
           <t>HOAI_DE_LP3_Entwurfsplanung</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -4397,8 +3960,6 @@
           <t>HOAI_DE_LP4_Genehmigungsplanung</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -4411,8 +3972,6 @@
           <t>HOAI_DE_LP5_Ausfuehrungsplanung</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -4425,8 +3984,6 @@
           <t>HOAI_DE_LP6_VorbereitungDerVergabe</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -4439,8 +3996,6 @@
           <t>HOAI_DE_LP7_MitwirkungBeiDerVergabe</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -4453,8 +4008,6 @@
           <t>HOAI_DE_LP8_Objektueberwachung</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -4467,8 +4020,6 @@
           <t>HOAI_DE_LP9_Objektbetreuung</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -4481,8 +4032,6 @@
           <t>AIA_US_SD_SchematicDesign</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -4495,8 +4044,6 @@
           <t>AIA_US_DD_DesignDevelopment</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -4509,8 +4056,6 @@
           <t>AIA_US_CD_ConstructionDocuments</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -4523,8 +4068,6 @@
           <t>AIA_US_BN_BiddingNegotiation</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -4537,8 +4080,6 @@
           <t>AIA_US_CA_ConstructionAdministration</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -4551,8 +4092,6 @@
           <t>SIA_CH_1_StrategischePlanung</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -4565,8 +4104,6 @@
           <t>SIA_CH_2_Vorstudien</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
@@ -4579,8 +4116,6 @@
           <t>SIA_CH_3_Projektierung</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
@@ -4593,8 +4128,6 @@
           <t>SIA_CH_4_Ausschreibung</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
@@ -4607,8 +4140,6 @@
           <t>SIA_CH_5_Realisierung</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
@@ -4621,8 +4152,6 @@
           <t>SIA_CH_6_Bewirtschaftung</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
@@ -4635,8 +4164,6 @@
           <t>GBDI_EndOfUse</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
@@ -4649,8 +4176,6 @@
           <t>Other_National</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4711,8 +4236,6 @@
           <t>0 Strategic definition</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -4725,8 +4248,6 @@
           <t>1 Preliminary studies</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -4739,8 +4260,6 @@
           <t>2 Concept design</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -4753,8 +4272,6 @@
           <t>3 Developed design</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -4767,8 +4284,6 @@
           <t>4 Technical design</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -4781,8 +4296,6 @@
           <t>5 Manufacturing and construction</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -4795,8 +4308,6 @@
           <t>6 Handover and commissioning</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -4809,8 +4320,6 @@
           <t>7 Operation and management</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -4823,8 +4332,6 @@
           <t>8 End of use, re-cycling</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4885,8 +4392,6 @@
           <t>Type 1 - early building model, concept design</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -4899,8 +4404,6 @@
           <t>Type 2 - building model, building permit design</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -4913,8 +4416,6 @@
           <t>Type 3 - as designed building model</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -4927,8 +4428,6 @@
           <t>Type 4 - fully detailed as designed or as built model</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4994,7 +4493,6 @@
           <t>International Property Measurement Standards. Global standard used to unify how buildings are measured worldwide.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -5012,7 +4510,6 @@
           <t>UK-based but internationally used rules for measuring buildings. Often aligned with IPMS.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -5030,7 +4527,6 @@
           <t>US national standard for measuring residential and commercial floor area. Defines how total area should be measured.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -5048,7 +4544,6 @@
           <t>Widely used in global commercial real estate; includes methods for leasing, international comparison, construction, volumetric measurement, and ENERGY STAR® compatibility.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -5066,7 +4561,6 @@
           <t>Regulatory method measuring GFA from exterior wall surfaces for energy compliance.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -5084,7 +4578,6 @@
           <t>Used by universities and facility managers; define gross, usable, and net areas on campuses.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -5102,7 +4595,6 @@
           <t>Practical methods used globally: measuring onsite or using architectural floor plans to calculate GFA.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -5115,8 +4607,6 @@
           <t>ISO 9836</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -5129,8 +4619,6 @@
           <t>IPMS 1 (whole building including external walls)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -5143,8 +4631,6 @@
           <t>IPMS 2 (building excluding external walls)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -5157,8 +4643,6 @@
           <t>IPMS 3.1 (occupier level, external)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -5171,8 +4655,6 @@
           <t>IPMS 3.2 (occupier level, internal)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5233,8 +4715,6 @@
           <t>ASHRAE169_1A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -5247,8 +4727,6 @@
           <t>ASHRAE169_2A</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -5261,8 +4739,6 @@
           <t>ASHRAE169_2B</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -5275,8 +4751,6 @@
           <t>ASHRAE169_3A</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -5289,8 +4763,6 @@
           <t>ASHRAE169_3B</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -5303,8 +4775,6 @@
           <t>ASHRAE169_3C</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -5317,8 +4787,6 @@
           <t>ASHRAE169_4A</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -5331,8 +4799,6 @@
           <t>ASHRAE169_4B</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -5345,8 +4811,6 @@
           <t>ASHRAE169_4C</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -5359,8 +4823,6 @@
           <t>ASHRAE169_5A</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -5373,8 +4835,6 @@
           <t>ASHRAE169_5B</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -5387,8 +4847,6 @@
           <t>ASHRAE169_5C</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -5401,8 +4859,6 @@
           <t>ASHRAE169_6A</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -5415,8 +4871,6 @@
           <t>ASHRAE169_6B</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -5429,8 +4883,6 @@
           <t>ASHRAE169_7</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -5443,8 +4895,6 @@
           <t>ASHRAE169_8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -5457,8 +4907,6 @@
           <t>IECC_1A</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -5471,8 +4919,6 @@
           <t>IECC_2A</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -5485,8 +4931,6 @@
           <t>IECC_2B</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -5499,8 +4943,6 @@
           <t>IECC_3A</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -5513,8 +4955,6 @@
           <t>IECC_3B</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -5527,8 +4967,6 @@
           <t>IECC_3C</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -5541,8 +4979,6 @@
           <t>IECC_4A</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -5555,8 +4991,6 @@
           <t>IECC_4B</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
@@ -5569,8 +5003,6 @@
           <t>IECC_4C</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
@@ -5583,8 +5015,6 @@
           <t>IECC_5A</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
@@ -5597,8 +5027,6 @@
           <t>IECC_5B</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
@@ -5611,8 +5039,6 @@
           <t>IECC_5C</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
@@ -5625,8 +5051,6 @@
           <t>IECC_6A</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
@@ -5639,8 +5063,6 @@
           <t>IECC_6B</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
@@ -5653,8 +5075,6 @@
           <t>IECC_7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
@@ -5667,8 +5087,6 @@
           <t>IECC_8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
@@ -5681,8 +5099,6 @@
           <t>KoppenGeiger_Af</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
@@ -5695,8 +5111,6 @@
           <t>KoppenGeiger_Am</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="2" t="inlineStr">
@@ -5709,8 +5123,6 @@
           <t>KoppenGeiger_Aw</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="2" t="inlineStr">
@@ -5723,8 +5135,6 @@
           <t>KoppenGeiger_BWh</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="2" t="inlineStr">
@@ -5737,8 +5147,6 @@
           <t>KoppenGeiger_BWk</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="2" t="inlineStr">
@@ -5751,8 +5159,6 @@
           <t>KoppenGeiger_BSh</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="2" t="inlineStr">
@@ -5765,8 +5171,6 @@
           <t>KoppenGeiger_BSk</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="2" t="inlineStr">
@@ -5779,8 +5183,6 @@
           <t>KoppenGeiger_Csa</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="2" t="inlineStr">
@@ -5793,8 +5195,6 @@
           <t>KoppenGeiger_Csb</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="2" t="inlineStr">
@@ -5807,8 +5207,6 @@
           <t>KoppenGeiger_Csc</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="2" t="inlineStr">
@@ -5821,8 +5219,6 @@
           <t>KoppenGeiger_Cwa</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="2" t="inlineStr">
@@ -5835,8 +5231,6 @@
           <t>KoppenGeiger_Cwb</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="2" t="inlineStr">
@@ -5849,8 +5243,6 @@
           <t>KoppenGeiger_Cwc</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="2" t="inlineStr">
@@ -5863,8 +5255,6 @@
           <t>KoppenGeiger_Cfa</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="2" t="inlineStr">
@@ -5877,8 +5267,6 @@
           <t>KoppenGeiger_Cfb</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="2" t="inlineStr">
@@ -5891,8 +5279,6 @@
           <t>KoppenGeiger_Cfc</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="2" t="inlineStr">
@@ -5905,8 +5291,6 @@
           <t>KoppenGeiger_Dsa</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="2" t="inlineStr">
@@ -5919,8 +5303,6 @@
           <t>KoppenGeiger_Dsb</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="2" t="inlineStr">
@@ -5933,8 +5315,6 @@
           <t>KoppenGeiger_Dsc</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="2" t="inlineStr">
@@ -5947,8 +5327,6 @@
           <t>KoppenGeiger_Dsd</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="2" t="inlineStr">
@@ -5961,8 +5339,6 @@
           <t>KoppenGeiger_Dwa</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="2" t="inlineStr">
@@ -5975,8 +5351,6 @@
           <t>KoppenGeiger_Dwb</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="2" t="inlineStr">
@@ -5989,8 +5363,6 @@
           <t>KoppenGeiger_Dwc</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="2" t="inlineStr">
@@ -6003,8 +5375,6 @@
           <t>KoppenGeiger_Dwd</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="2" t="inlineStr">
@@ -6017,8 +5387,6 @@
           <t>KoppenGeiger_Dfa</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="2" t="inlineStr">
@@ -6031,8 +5399,6 @@
           <t>KoppenGeiger_Dfb</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="2" t="inlineStr">
@@ -6045,8 +5411,6 @@
           <t>KoppenGeiger_Dfc</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="2" t="inlineStr">
@@ -6059,8 +5423,6 @@
           <t>KoppenGeiger_Dfd</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="2" t="inlineStr">
@@ -6073,8 +5435,6 @@
           <t>KoppenGeiger_ET</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="2" t="inlineStr">
@@ -6087,8 +5447,6 @@
           <t>KoppenGeiger_EF</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="2" t="inlineStr">
@@ -6101,8 +5459,6 @@
           <t>Other_National</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="2" t="inlineStr">
@@ -6115,8 +5471,6 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6182,7 +5536,6 @@
           <t>Minor expected ground shaking.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -6200,7 +5553,6 @@
           <t>Moderate expected ground shaking for standard buildings.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -6218,7 +5570,6 @@
           <t>Moderate to severe expected ground shaking for standard buildings, and moderate for higher-risk buildings.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -6236,7 +5587,6 @@
           <t>Severe and destructive expected ground shaking, often associated with poorer soil conditions but not near major faults.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -6254,7 +5604,6 @@
           <t>Severe expected ground shaking in areas near major active faults.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -6272,7 +5621,6 @@
           <t>Severe expected ground shaking in areas near major active faults for high-risk buildings.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6333,8 +5681,6 @@
           <t>Single family houses (SFH)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -6347,8 +5693,6 @@
           <t>Multifamily houses (MFH)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -6361,8 +5705,6 @@
           <t>Apartment blocks (ABL)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -6375,8 +5717,6 @@
           <t>Offices (OFF)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -6389,8 +5729,6 @@
           <t>Trade (TRA)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -6403,8 +5741,6 @@
           <t>Education (EDU)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -6417,8 +5753,6 @@
           <t>Health (HEA)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -6431,8 +5765,6 @@
           <t>Hotels and Restaurants (HOR)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -6445,8 +5777,6 @@
           <t>Other non-residential buildings (OTH)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6512,7 +5842,6 @@
           <t>Building element classification for the United States.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -6530,7 +5859,6 @@
           <t>Building element classification for Canada.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -6548,7 +5876,6 @@
           <t>Building element classification for the United Kingdom.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -6566,7 +5893,6 @@
           <t>Building element classification for Denmark.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -6584,7 +5910,6 @@
           <t>Building element classification for Sweden.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -6602,7 +5927,6 @@
           <t>Building element classification for Finland.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -6620,7 +5944,6 @@
           <t>Building element classification for Norway.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -6638,7 +5961,6 @@
           <t>Building element classification for Germany.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -6656,7 +5978,6 @@
           <t>Building element classification for France.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -6674,7 +5995,6 @@
           <t>Building element classification for Switzerland.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -6692,7 +6012,6 @@
           <t>Building element classification for the Netherlands.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -6710,7 +6029,6 @@
           <t>Building element classification for Austria.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -6728,7 +6046,6 @@
           <t>Building element classification for Italy.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -6746,7 +6063,6 @@
           <t>Building element classification for Spain.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -6764,7 +6080,6 @@
           <t>Building element classification for Australia.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -6782,7 +6097,6 @@
           <t>Building element classification for Japan.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -6800,7 +6114,6 @@
           <t>Building element classification for Brazil.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -6818,7 +6131,6 @@
           <t>Building element classification for the Czech Republic.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -6836,7 +6148,6 @@
           <t>International framework for classification of construction objects.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6902,7 +6213,6 @@
           <t>Primary (top-level) hierarchical category of the custom or national building element classification.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -6920,7 +6230,6 @@
           <t>Secondary hierarchical category of the custom or national building element classification.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -6938,7 +6247,6 @@
           <t>The tertiary hierarchical category of the custom or national building element classification.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -6956,7 +6264,6 @@
           <t>The quaternary (lowest-level) hierarchical category of the custom or national building element classification.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7155,8 +6462,6 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -7169,8 +6474,6 @@
           <t>Concrete_InSitu</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -7183,8 +6486,6 @@
           <t>Concrete_Precast</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -7197,8 +6498,6 @@
           <t>Concrete_PostTensioned</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -7211,8 +6510,6 @@
           <t>Concrete_Frame</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -7225,8 +6522,6 @@
           <t>Concrete_Mass</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -7239,8 +6534,6 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -7253,8 +6546,6 @@
           <t>Steel_Frame</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -7267,8 +6558,6 @@
           <t>Steel_Composite</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -7281,8 +6570,6 @@
           <t>Steel_Precast</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -7295,8 +6582,6 @@
           <t>Timber</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -7309,8 +6594,6 @@
           <t>Timber_Frame</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -7323,8 +6606,6 @@
           <t>Timber_Massive</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -7337,8 +6618,6 @@
           <t>Timber_CLT</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -7351,8 +6630,6 @@
           <t>Timber_Glulam</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -7365,8 +6642,6 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -7379,8 +6654,6 @@
           <t>Masonry_MassiveBrick</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -7393,8 +6666,6 @@
           <t>Masonry_Mixed</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -7407,8 +6678,6 @@
           <t>Mixed_ConcreteSteel</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -7421,8 +6690,6 @@
           <t>Mixed_ConcreteTimber</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -7435,8 +6702,6 @@
           <t>Mixed_SteelTimber</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -7449,8 +6714,6 @@
           <t>Mixed_ConcreteMasonry</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -7463,8 +6726,6 @@
           <t>Mixed_Other</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -7477,8 +6738,6 @@
           <t>Other_Unknown</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7544,7 +6803,6 @@
           <t>Stable rock formations, often characterized by layered or planar structures.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -7562,7 +6820,6 @@
           <t>A mixture of gravel and sand with high load-bearing capacity.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -7580,7 +6837,6 @@
           <t>Granular material composed of finely divided rock and mineral particles.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -7598,7 +6854,6 @@
           <t>Sand containing a significant portion of silt particles, affecting drainage.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -7616,7 +6871,6 @@
           <t>Fine-grained natural soil material that is plastic when wet.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -7634,7 +6888,6 @@
           <t>Clay with high water content and lower shear strength compared to standard clay.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7700,7 +6953,6 @@
           <t>Spread foundation - Pad Footings (Isolated) according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -7718,7 +6970,6 @@
           <t>Spread foundation - Strip Footings (Continuous) according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -7736,7 +6987,6 @@
           <t>Spread foundation - Raft Foundations (Mat) according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -7754,7 +7004,6 @@
           <t>Piled Foundations - Displacement Piles (Driven) according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -7772,7 +7021,6 @@
           <t>Piled Foundations - Replacement Piles (Bored/Drilled) according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -7790,7 +7038,6 @@
           <t>Other Geotechnical Structures - Retaining Walls according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -7808,7 +7055,6 @@
           <t>Other Geotechnical Structures - Deep Shafts (Caissons) according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -7826,7 +7072,6 @@
           <t>Other Geotechnical Structures - Ground Anchors according to Eurocode 7.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -7844,7 +7089,6 @@
           <t>Shallow Foundations - Isolated (Spread) Footings according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -7862,7 +7106,6 @@
           <t>Shallow Foundations - Combined Footings according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -7880,7 +7123,6 @@
           <t>Shallow Foundations - Strip / Continuous Footings according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -7898,7 +7140,6 @@
           <t>Shallow Foundations - Raft / Mat Foundations according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -7916,7 +7157,6 @@
           <t>Shallow Foundations - Slab‑on‑Grade Foundations according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -7934,7 +7174,6 @@
           <t>Deep Foundations - Driven Piles according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -7952,7 +7191,6 @@
           <t>Deep Foundations - Drilled Shafts / Caissons according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -7970,7 +7208,6 @@
           <t>Deep Foundations - Piers according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -7988,7 +7225,6 @@
           <t>Specialized Foundations - Frost‑Protected Foundations according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -8006,7 +7242,6 @@
           <t>Specialized Foundations - Soil‑Specific Foundations (Clay, Sand, Silt, Rock) according to IBC Chapter 18.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8072,7 +7307,6 @@
           <t>European Union Energy Performance Certificate - mandatory across the EU, grades usually A to G</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -8090,7 +7324,6 @@
           <t>US Environmental Protection Agency standard - 1-100 score</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -8108,7 +7341,6 @@
           <t>National Australian Built Environment Rating System - widely used in Australia and expanding to the UK</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -8126,7 +7358,6 @@
           <t>Haute Qualité Environnementale - standard in France</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -8144,7 +7375,6 @@
           <t>German Sustainable Building Council standard</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -8162,7 +7392,6 @@
           <t>Standard in Australia, New Zealand, and South Africa</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -8180,7 +7409,6 @@
           <t>Singapore's standard, widely used in Southeast Asia</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -8198,7 +7426,6 @@
           <t>Comprehensive Assessment System for Built Environment Efficiency - Japan</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -8216,7 +7443,6 @@
           <t>Leadership in Energy and Environmental Design - heavily used in the Americas and globally</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -8234,7 +7460,6 @@
           <t>Building Research Establishment Environmental Assessment Method - heavily used in the UK and globally</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -8252,7 +7477,6 @@
           <t>Excellence in Design for Greater Efficiencies - IFC standard, very common in emerging markets</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -8270,7 +7494,6 @@
           <t>Often paired with LEED/BREEAM, focuses on human health but intersects with building performance</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -8288,7 +7511,6 @@
           <t>Any other building energy certification system not listed above</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -8306,7 +7528,6 @@
           <t>No energy classification or certification for this building</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8367,8 +7588,6 @@
           <t>EPBD (EU)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -8381,8 +7600,6 @@
           <t>EN ISO 52000-1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -8395,8 +7612,6 @@
           <t>IECC (US)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -8409,8 +7624,6 @@
           <t>ASHRAE 90.1 (US)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -8423,8 +7636,6 @@
           <t>ASHRAE 189.1 (US)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -8437,8 +7648,6 @@
           <t>OIB-Richtlinie 6 (AT)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -8451,8 +7660,6 @@
           <t>GEG (DE)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -8465,8 +7672,6 @@
           <t>SIA 380/1 (CH)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -8479,8 +7684,6 @@
           <t>RE2020 (FR)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -8493,8 +7696,6 @@
           <t>CTE DB-HE (ES)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -8507,8 +7708,6 @@
           <t>Bouwbesluit / BENG (NL)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -8521,8 +7720,6 @@
           <t>Part L (UK)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -8535,8 +7732,6 @@
           <t>Other national</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -8549,8 +7744,6 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8611,8 +7804,6 @@
           <t>Natural Gas</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -8625,8 +7816,6 @@
           <t>Coal</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -8639,8 +7828,6 @@
           <t>Oil/Petroleum</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -8653,8 +7840,6 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -8667,8 +7852,6 @@
           <t>Solar Energy (Photovoltaic and Thermal)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -8681,8 +7864,6 @@
           <t>Wind Energy</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -8695,8 +7876,6 @@
           <t>Hydropower</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -8709,8 +7888,6 @@
           <t>Geothermal Energy</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -8723,8 +7900,6 @@
           <t>Aerothermal Energy</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -8737,8 +7912,6 @@
           <t>Biomass (Wood, Pellets)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -8751,8 +7924,6 @@
           <t>Waste Heat</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8818,7 +7989,6 @@
           <t>North-facing</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -8836,7 +8006,6 @@
           <t>South-facing</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -8854,7 +8023,6 @@
           <t>East-facing</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -8872,7 +8040,6 @@
           <t>West-facing</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -8890,7 +8057,6 @@
           <t>Northeast-facing</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -8908,7 +8074,6 @@
           <t>Northwest-facing</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -8926,7 +8091,6 @@
           <t>Southeast-facing</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -8944,7 +8108,6 @@
           <t>Southwest-facing</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9005,8 +8168,6 @@
           <t>ABNT NBR 12.721 (Brazil), Área Real Global / Área Construída</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -9019,8 +8180,6 @@
           <t>BOMA Z65.3 / CSA Z249 (Canada), Gross Building Area (GBA)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -9033,8 +8192,6 @@
           <t>Building Standards Act (Japan), Nobe-yuka-menseki (Total Floor Area)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -9047,8 +8204,6 @@
           <t>Buildings Department (Hong Kong), Gross Floor Area (GFA)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -9061,8 +8216,6 @@
           <t>Code de l'urbanisme (France), Surface de Plancher (SDP)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -9075,8 +8228,6 @@
           <t>DIN 277 (Germany), Brutto-Grundfläche (BGF)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -9089,8 +8240,6 @@
           <t>Dubai Land Department / RICS (UAE), Gross Floor Area (GFA)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -9103,8 +8252,6 @@
           <t>GB/T 50353 (China), Gross Floor Area (GFA) / Jianzhu Mianji</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -9117,8 +8264,6 @@
           <t>IPMS 1 / BOMA (International / USA), Gross Building Area (GBA)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -9131,8 +8276,6 @@
           <t>IRAM (Argentina), Superficie Cubierta Total</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -9145,8 +8288,6 @@
           <t>IS 3861 / RERA (India), Plinth Area / Super Built-up Area</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -9159,8 +8300,6 @@
           <t>MOMRA / Saudi Building Code (Saudi Arabia), Total Built-up Area (TBA)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -9173,8 +8312,6 @@
           <t>NBC (Philippines), Gross Floor Area (GFA)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -9187,8 +8324,6 @@
           <t>NEN 2580 (Netherlands), Bruto Vloeroppervlak (BVO)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -9201,8 +8336,6 @@
           <t>NS 3940 (Norway), Bruttoareal (BTA)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -9215,8 +8348,6 @@
           <t>ÖNORM B 1800 (Austria), Brutto-Grundfläche (BGF)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -9229,8 +8360,6 @@
           <t>Property Council of Australia (Australia), Gross Floor Area (GFA)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -9243,8 +8372,6 @@
           <t>QCVN 03:2012/BXD (Vietnam), Gross Floor Area (GFA) / Dien tich san</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -9257,8 +8384,6 @@
           <t>Real Decreto 1020/1993 (Spain), Superficie Construida</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -9271,8 +8396,6 @@
           <t>Reglamento de Construcciones (Mexico), Superficie de Construcción</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -9285,8 +8408,6 @@
           <t>RICS (UK), Type 1: GEA (Gross External Area)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -9299,8 +8420,6 @@
           <t>RICS (UK), Type 2: GIA (Gross Internal Area)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -9313,8 +8432,6 @@
           <t>SANS 10400 (South Africa), Gross Floor Area (GFA)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -9327,8 +8444,6 @@
           <t>SFS 5139 (Finland), Bruttoala (BrlA)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
@@ -9341,8 +8456,6 @@
           <t>SIA 416 (Switzerland), Bruttogeschossfläche (BGF) / Surface de plancher brute (SPB)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
@@ -9355,8 +8468,6 @@
           <t>SNI 03-1728 (Indonesia), Luas Lantai Bangunan (Building Floor Area)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
@@ -9369,8 +8480,6 @@
           <t>SNiP / SP 54.13330 (Russia), Obshchaya Ploshchad (Total Area)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
@@ -9383,8 +8492,6 @@
           <t>SS 21054 (Sweden), Bruttoarea (BTA)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
@@ -9397,8 +8504,6 @@
           <t>Turkish Standard TS 01 (Turkey), Brüt Alan (Gross Area)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
@@ -9411,8 +8516,6 @@
           <t>UNI 11136 (Italy), Superficie Lorda (SL)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
@@ -9425,8 +8528,6 @@
           <t>URA (Singapore), Gross Floor Area (GFA)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9492,7 +8593,6 @@
           <t>shares structure, inside envelope</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -9510,7 +8610,6 @@
           <t>structurally independent</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -9523,8 +8622,6 @@
           <t>Unconditioned space</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -9537,8 +8634,6 @@
           <t>Circulation</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -9551,8 +8646,6 @@
           <t>Technical space</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -9565,8 +8658,6 @@
           <t>Ancillary external buildings</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -9579,8 +8670,6 @@
           <t>None of the above</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9646,7 +8735,6 @@
           <t>whole replacements only</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -9664,7 +8752,6 @@
           <t>fractional replacements allowed</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -9682,7 +8769,6 @@
           <t>rule not declared</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14363,8 +13449,6 @@
           <t>OKOBAUDAT_20.23.050</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -14377,8 +13461,6 @@
           <t>OKOBAUDAT_20.24.070</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -14391,8 +13473,6 @@
           <t>habitat2030_BIGTEN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -14405,8 +13485,6 @@
           <t>IBU_Data</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -14419,8 +13497,6 @@
           <t>EC3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -14433,8 +13509,6 @@
           <t>Ecoinvent</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -14447,8 +13521,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14514,7 +13586,6 @@
           <t>recycled content approach, ecoinvent cut-off</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -14532,7 +13603,6 @@
           <t>ecoinvent system model aligned with EN 15804</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -14550,7 +13620,6 @@
           <t>allocation at the point of substitution</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -14568,7 +13637,6 @@
           <t>marginal, market-driven modelling</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14634,7 +13702,6 @@
           <t>shares weighted by fossil global warming potential of modules A1 to A3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -14652,7 +13719,6 @@
           <t>shares weighted by mass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -14670,7 +13736,6 @@
           <t>shares not weighted</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14731,8 +13796,6 @@
           <t>Static (impacts not distributed over time)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -14745,8 +13808,6 @@
           <t>Dynamic (impacts distributed over time)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -14759,8 +13820,6 @@
           <t>Probabilistic</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -14773,8 +13832,6 @@
           <t>Prospective</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14840,7 +13897,6 @@
           <t>full allocation to the building of energy storage components and of all other system parts</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -14858,7 +13914,6 @@
           <t>full allocation of energy storage components; other system parts allocated in proportion to the share of captured or generated energy used for self-consumption</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -14876,7 +13931,6 @@
           <t>full allocation of energy storage components; components integrated into the building envelope and forming its surface allocated in full, with the remaining embodied emissions allocated in proportion to the share used for self-consumption</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14942,7 +13996,6 @@
           <t>the submission covers a single building</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -14960,7 +14013,6 @@
           <t>the whole complex of buildings constitutes one single assessment</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -14978,7 +14030,6 @@
           <t>the total is divided proportionately between the owner building units</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -14996,7 +14047,6 @@
           <t>allocated on the basis of the relative shares of parking spaces designated to each building</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -15014,7 +14064,6 @@
           <t>a national rule, stated in the assessor note</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15080,7 +14129,6 @@
           <t>an outermost region within the meaning of Article 349 TFEU</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -15098,7 +14146,6 @@
           <t>default values used to fill data gaps where no other type of data is available</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -15116,7 +14163,6 @@
           <t>default values used where it is necessary to simplify the calculation</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -15134,7 +14180,6 @@
           <t>stated in the assessor note</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15200,7 +14245,6 @@
           <t>nothing left out, the result is a complete assessment</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -15218,7 +14262,6 @@
           <t>parts of life-cycle stages left out</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -15236,7 +14279,6 @@
           <t>parts of the scope of building components left out</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -15254,7 +14296,6 @@
           <t>parts of life-cycle stages and parts of the scope of building components left out</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15320,7 +14361,6 @@
           <t>no operational energy calculated</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -15338,7 +14378,6 @@
           <t>no forward-looking factors; the factors of the base year apply over the whole period</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -15356,7 +14395,6 @@
           <t>forward-looking emission factors, justified, consistent and clearly defined for the whole reference study period</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15422,7 +14460,6 @@
           <t>Calculates impacts by summing individual process steps.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -15440,7 +14477,6 @@
           <t>Input-Output based modeling using economic data.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -15458,7 +14494,6 @@
           <t>Combines both process-based and I-O based methodologies.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -15476,7 +14511,6 @@
           <t>Alternative LCA modeling methodology.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16274,7 +15308,6 @@
           <t>Covers modules A1–A3.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -16292,7 +15325,6 @@
           <t>Covers modules A1–A3 plus others.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -16310,7 +15342,6 @@
           <t>Covers modules A1–C4.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -16328,7 +15359,6 @@
           <t>Covers modules A1–C4 and includes module D.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -16346,7 +15376,6 @@
           <t>Focuses specifically on the production stage processes.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16407,8 +15436,6 @@
           <t>EN 15804:2012+A1:2013</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -16421,8 +15448,6 @@
           <t>EN 15804:2012+A2:2019</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -16435,8 +15460,6 @@
           <t>EN 15978:2026</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -16449,8 +15472,6 @@
           <t>US EPA TRACI 2.1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -16463,8 +15484,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16530,7 +15549,6 @@
           <t>Neutral accounting (no sequestration/no emission)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -16548,7 +15566,6 @@
           <t>Credit at start / burden at end of life</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -16561,8 +15578,6 @@
           <t>Dynamic LCA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -16575,8 +15590,6 @@
           <t>Ton-Year Accounting or Discounting Method</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -16589,8 +15602,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16651,8 +15662,6 @@
           <t>Extrapolation from Construction Type Land Use Area</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -16665,8 +15674,6 @@
           <t>Manual Approximation</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -16679,8 +15686,6 @@
           <t>BIM Model</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -16693,8 +15698,6 @@
           <t>Design Estimates/ Manual Takeoff from Design Documentation</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -16707,8 +15710,6 @@
           <t>Construction Estimate/Contractors Bill of Materials</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -16721,8 +15722,6 @@
           <t>As-Built</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -16735,8 +15734,6 @@
           <t>Other Data Source</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16797,8 +15794,6 @@
           <t>Above ground</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -16811,8 +15806,6 @@
           <t>Below ground</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16873,8 +15866,6 @@
           <t>0 Treatment and demolition works &amp; Facilitating works</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -16887,8 +15878,6 @@
           <t>1 Sub-structure</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -16901,8 +15890,6 @@
           <t>2 Super structure</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -16915,8 +15902,6 @@
           <t>3 Finishes</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -16929,8 +15914,6 @@
           <t>4 FF&amp;E</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -16943,8 +15926,6 @@
           <t>5 Building Services/ MEP</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -16957,8 +15938,6 @@
           <t>6 Pre-fabricated buildings and units</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -16971,8 +15950,6 @@
           <t>7 Works to existing buildings</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -16985,8 +15962,6 @@
           <t>8 External works</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -16999,7 +15974,6 @@
           <t>0.1 Treatment and demolition works &amp; Facilitating works</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>0</t>
@@ -17017,7 +15991,6 @@
           <t>1.1 Foundations and piling</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>1</t>
@@ -17035,7 +16008,6 @@
           <t>1.2 Basement retaining walls and lowest slab</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>1</t>
@@ -17053,7 +16025,6 @@
           <t>2.1 Frame</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>2</t>
@@ -17071,7 +16042,6 @@
           <t>2.2 Upper floors</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>2</t>
@@ -17089,7 +16059,6 @@
           <t>2.3 Roof</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>2</t>
@@ -17107,7 +16076,6 @@
           <t>2.4 Stairs, ramps and safety guarding</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>2</t>
@@ -17125,7 +16093,6 @@
           <t>2.5 External envelope including roof finishes</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>2</t>
@@ -17143,7 +16110,6 @@
           <t>2.6 Windows and ext doors</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>2</t>
@@ -17161,7 +16127,6 @@
           <t>2.7 Internal walls</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>2</t>
@@ -17179,7 +16144,6 @@
           <t>2.8 Internal doors</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>2</t>
@@ -17197,7 +16161,6 @@
           <t>3.1 Wall finishes</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>3</t>
@@ -17215,7 +16178,6 @@
           <t>3.2 Floor finishes</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>3</t>
@@ -17233,7 +16195,6 @@
           <t>3.3 Ceiling finishes</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>3</t>
@@ -17251,7 +16212,6 @@
           <t>4.1 General FF&amp;E</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>4</t>
@@ -17269,7 +16229,6 @@
           <t>4.2 Kitchen equipment</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>4</t>
@@ -17287,7 +16246,6 @@
           <t>4.3 Special equipment</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>4</t>
@@ -17305,7 +16263,6 @@
           <t>4.4 Loose FF&amp;E</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>4</t>
@@ -17323,7 +16280,6 @@
           <t>4.5 IT</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>4</t>
@@ -17341,7 +16297,6 @@
           <t>4.6 Audio and visual</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>4</t>
@@ -17359,7 +16314,6 @@
           <t>5.1 Public Health</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>5</t>
@@ -17377,7 +16331,6 @@
           <t>5.2 Heating, Ventilation and Cooling (HVAC)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>5</t>
@@ -17395,7 +16348,6 @@
           <t>5.3 Electrical installations</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>5</t>
@@ -17413,7 +16365,6 @@
           <t>5.4 On site renewable energy generation</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>5</t>
@@ -17431,7 +16382,6 @@
           <t>5.5 Systems including Life safety, Fuel, Lift, Waste, and Builders work</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>5</t>
@@ -17449,7 +16399,6 @@
           <t>6.0 Pre-fabricated buildings and building units</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>6</t>
@@ -17467,7 +16416,6 @@
           <t>7.1 Alterations</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>7</t>
@@ -17485,7 +16433,6 @@
           <t>7.2 Repairs, Cleaning and Renovation</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>7</t>
@@ -17503,7 +16450,6 @@
           <t>7.3 Damp-proof courses/fungus and beetle eradication</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>7</t>
@@ -17521,7 +16467,6 @@
           <t>8.1 Roads, paths, pavings, surfaces, Fencing, railings, walls, External fixtures</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>8</t>
@@ -17539,7 +16484,6 @@
           <t>8.2 Soft landscape, planting, irrigation</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>8</t>
@@ -17557,7 +16501,6 @@
           <t>8.3 External drainage, External services, Minor building works</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>8</t>
@@ -17575,7 +16518,6 @@
           <t>0.1.1 Toxic/contaminated material treatment &amp; Demolition works</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>0.1</t>
@@ -17593,7 +16535,6 @@
           <t>0.1.2 Facilitating works</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>0.1</t>
@@ -17611,7 +16552,6 @@
           <t>1.1.1 Foundations and piling</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -17629,7 +16569,6 @@
           <t>1.2.1 Lowest slab</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -17647,7 +16586,6 @@
           <t>1.2.2 Suspended slabs</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -17665,7 +16603,6 @@
           <t>1.2.3 Basement retaining walls</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -17683,7 +16620,6 @@
           <t>2.1.1 Frame (vertical) - columns/ structural walls &amp; braces</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -17701,7 +16637,6 @@
           <t>2.1.2 Frame (Horizontal) - beams, joists &amp; braces</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -17719,7 +16654,6 @@
           <t>2.2.1 Upper floor - structural slabs</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -17737,7 +16671,6 @@
           <t>2.2.2 Upper floor - non-structural slabs</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -17755,7 +16688,6 @@
           <t>2.3.1 Roof - structural slabs</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -17773,7 +16705,6 @@
           <t>2.4.1 Stairs</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>2.4</t>
@@ -17791,7 +16722,6 @@
           <t>2.4.2 Ramps</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>2.4</t>
@@ -17809,7 +16739,6 @@
           <t>2.4.3 Safety and access ladders, chutes, slides and guarding</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>2.4</t>
@@ -17827,7 +16756,6 @@
           <t>2.5.1 External - opaque envelope</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -17845,7 +16773,6 @@
           <t>2.5.2 External - full height glazing systems</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -17863,7 +16790,6 @@
           <t>2.5.3 External - roof finishes/coverings</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -17881,7 +16807,6 @@
           <t>2.5.4 External - safety systems</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -17899,7 +16824,6 @@
           <t>2.6.1 Windows - vertical</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -17917,7 +16841,6 @@
           <t>2.6.2 Windows - roof or horizontal</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -17935,7 +16858,6 @@
           <t>2.6.3 External doors</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -17953,7 +16875,6 @@
           <t>2.7.1 Internal walls - solid</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -17971,7 +16892,6 @@
           <t>2.7.2 Internal walls - non-structural glazed walls, windows and vision panels</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -17989,7 +16909,6 @@
           <t>3.2.1 Raised access floor or specialist sprung floors</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -18007,7 +16926,6 @@
           <t>3.2.2 Non-structural screed</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -18025,7 +16943,6 @@
           <t>3.2.3 Floor finishes</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -18043,7 +16960,6 @@
           <t>5.1.1 Sanitaryware</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -18061,7 +16977,6 @@
           <t>5.1.2 Cold water systems</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -18079,7 +16994,6 @@
           <t>5.1.3 Drainage and rainwater</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -18097,7 +17011,6 @@
           <t>5.2.1 Space heating and hot water</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -18115,7 +17028,6 @@
           <t>5.2.2 Dedicated cooling installations</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -18133,7 +17045,6 @@
           <t>5.2.3 Air movement</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -18151,7 +17062,6 @@
           <t>5.2.4 Ventilation air terminals, ductwork and fire safety</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -18169,7 +17079,6 @@
           <t>5.3.1 Lighting</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -18187,7 +17096,6 @@
           <t>5.3.2 Electrical services for power, communications, security, IT and fire detection</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -18205,7 +17113,6 @@
           <t>5.4.1 On site renewable energy generation</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -18223,7 +17130,6 @@
           <t>5.5.1 Life safety</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -18241,7 +17147,6 @@
           <t>5.5.2 Fuel installations</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -18259,7 +17164,6 @@
           <t>5.5.3 Lift and conveyor installations</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -18277,7 +17181,6 @@
           <t>5.5.4 Specialised and communal waste disposal</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -18295,7 +17198,6 @@
           <t>5.5.5 Specialist installations &amp; maintenance</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -18313,7 +17215,6 @@
           <t>5.5.6 Builders work in connection with services</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -18331,7 +17232,6 @@
           <t>8.1.1 Roads, paths, pavings, surfaces</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>8.1</t>
@@ -18349,7 +17249,6 @@
           <t>8.1.2 Fencing, railings, walls</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>8.1</t>
@@ -18367,7 +17266,6 @@
           <t>8.1.3 External fixtures</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>8.1</t>
@@ -18385,7 +17283,6 @@
           <t>8.3.1 External drainage</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>8.3</t>
@@ -18403,7 +17300,6 @@
           <t>8.3.2 External services</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>8.3</t>
@@ -18421,7 +17317,6 @@
           <t>8.3.3 Minor building works, ancillary</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>8.3</t>
@@ -20406,7 +19301,6 @@
           <t>Bio-based materials</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -20424,7 +19318,6 @@
           <t>Bio-based materials</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -20442,7 +19335,6 @@
           <t>Bio-based materials</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -20460,7 +19352,6 @@
           <t>Fossil-based materials</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -20478,7 +19369,6 @@
           <t>Fossil-based materials</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -20496,7 +19386,6 @@
           <t>Fossil-based materials</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -20514,7 +19403,6 @@
           <t>Metal materials</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -20532,7 +19420,6 @@
           <t>Metal materials</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -20550,7 +19437,6 @@
           <t>Metal materials</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -20568,7 +19454,6 @@
           <t>Metal materials</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -20586,7 +19471,6 @@
           <t>Non-metallic minerals</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -20604,7 +19488,6 @@
           <t>Non-metallic minerals</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -20622,7 +19505,6 @@
           <t>Non-metallic minerals</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -20640,7 +19522,6 @@
           <t>Non-metallic minerals</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -20658,7 +19539,6 @@
           <t>Non-metallic minerals</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -20676,7 +19556,6 @@
           <t>Undefined materials</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20742,7 +19621,6 @@
           <t>declaration of performance and conformity under the Construction Products Regulation</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -20760,7 +19638,6 @@
           <t>data issued under ecodesign or energy labelling legislation</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -20778,7 +19655,6 @@
           <t>assessment of this project, not issued under those rules</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -20796,7 +19672,6 @@
           <t>assessment of this product, not issued under those rules</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -20814,7 +19689,6 @@
           <t>sectoral or industry average</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -20832,7 +19706,6 @@
           <t>background database value</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -20850,7 +19723,6 @@
           <t>conservative national default</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20916,7 +19788,6 @@
           <t>the declaration describes this product</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -20934,7 +19805,6 @@
           <t>a sectoral average covering it</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -20952,7 +19822,6 @@
           <t>a different product used as a stand-in</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -20970,7 +19839,6 @@
           <t>the same product, another region</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -20988,7 +19856,6 @@
           <t>the same product, outside the validity of its declaration</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -21006,7 +19873,6 @@
           <t>a broad reference, not a match</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -21024,7 +19890,6 @@
           <t>the relationship cannot be established</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36714,7 +35579,6 @@
           <t>a building that exists or is being built</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -36732,7 +35596,6 @@
           <t>a representative building of a stock model</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -36750,7 +35613,6 @@
           <t>an alternative design of the same building</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -36768,7 +35630,6 @@
           <t>a generated variation</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36829,8 +35690,6 @@
           <t>Imperial Units System (IP, USA)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -36843,8 +35702,6 @@
           <t>Metric, International Units System (SI)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36905,8 +35762,6 @@
           <t>New Construction</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -36919,8 +35774,6 @@
           <t>Tenant Improvements</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -36933,8 +35786,6 @@
           <t>Minor Renovation (without addition)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -36947,8 +35798,6 @@
           <t>Major Renovation (with addition)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/translators/templates/translator_template_v2.0.0.xlsx
+++ b/translators/templates/translator_template_v2.0.0.xlsx
@@ -57,6 +57,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialDataType" sheetId="48" state="visible" r:id="rId48"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialEPDMatch" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeclaredUnit" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FloorLevel" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -106,7 +107,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -125,17 +126,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00a3d3bd"/>
+        <fgColor rgb="00189d7e"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00a9d2f6"/>
+        <fgColor rgb="003592e3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00d8e6e2"/>
+        <fgColor rgb="00e9f7fe"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0031658d"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009dd2f3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00bcc4c2"/>
       </patternFill>
     </fill>
     <fill>
@@ -173,7 +189,7 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
@@ -181,29 +197,35 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="6"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="8">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="11">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="6"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="8"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="5"/>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="13">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
     <cellStyle name="AttributeName" xfId="1" hidden="0"/>
     <cellStyle name="Info" xfId="2" hidden="0"/>
@@ -211,9 +233,12 @@
     <cellStyle name="Required" xfId="4" hidden="0"/>
     <cellStyle name="Recommended" xfId="5" hidden="0"/>
     <cellStyle name="Optional" xfId="6" hidden="0"/>
-    <cellStyle name="RowHeader" xfId="7" hidden="0"/>
-    <cellStyle name="EditableValue" xfId="8" hidden="0"/>
-    <cellStyle name="Disabled" xfId="9" hidden="0"/>
+    <cellStyle name="Strongly recommended" xfId="7" hidden="0"/>
+    <cellStyle name="Suggested" xfId="8" hidden="0"/>
+    <cellStyle name="Automatic" xfId="9" hidden="0"/>
+    <cellStyle name="RowHeader" xfId="10" hidden="0"/>
+    <cellStyle name="EditableValue" xfId="11" hidden="0"/>
+    <cellStyle name="Disabled" xfId="12" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4865,7 +4890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5027,6 +5052,20 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9899,7 +9938,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9923,7 +9962,7 @@
           <t>RecordType</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9947,7 +9986,7 @@
           <t>ProjectUnits</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9971,9 +10010,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
@@ -9995,7 +10034,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10019,9 +10058,9 @@
           <t>ConstructionType</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
@@ -10043,9 +10082,9 @@
           <t>Country</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -10067,7 +10106,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10091,9 +10130,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -10115,9 +10154,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
@@ -10139,7 +10178,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10163,9 +10202,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
@@ -10187,9 +10226,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
@@ -10211,9 +10250,9 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -10235,7 +10274,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10259,9 +10298,9 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -10283,9 +10322,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -10307,9 +10346,9 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
@@ -10331,9 +10370,9 @@
           <t>ProjectPhase</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
@@ -10379,7 +10418,7 @@
           <t>AssessmentType_EN15978</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -10403,9 +10442,9 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
@@ -10427,7 +10466,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10451,7 +10490,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10475,7 +10514,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10499,7 +10538,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10523,7 +10562,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10547,7 +10586,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10571,7 +10610,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10595,7 +10634,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10619,7 +10658,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10643,9 +10682,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
@@ -10667,7 +10706,7 @@
           <t>GFAMeasurementMethod</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -10691,9 +10730,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -10715,9 +10754,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
@@ -10739,7 +10778,7 @@
           <t>ClimateZone</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -10763,9 +10802,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -10787,9 +10826,9 @@
           <t>FEMASeismicActivity</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -10811,9 +10850,9 @@
           <t>BuildingTypology</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
@@ -10835,9 +10874,9 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
@@ -10859,7 +10898,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10883,7 +10922,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10907,9 +10946,9 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
@@ -10931,7 +10970,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10955,9 +10994,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
@@ -10979,7 +11018,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -11003,7 +11042,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -11027,9 +11066,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
@@ -11051,9 +11090,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
@@ -11075,9 +11114,9 @@
           <t>BuildingClassificationCode</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
@@ -11099,9 +11138,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
@@ -11123,9 +11162,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
@@ -11147,9 +11186,9 @@
           <t>BuildingElementClassificationTier</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
@@ -11171,7 +11210,7 @@
           <t>BuildingStructureType</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -11195,9 +11234,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
@@ -11219,9 +11258,9 @@
           <t>SoilType</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
@@ -11243,9 +11282,9 @@
           <t>FoundationType</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
@@ -11267,9 +11306,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
@@ -11291,9 +11330,9 @@
           <t>BuildingEnergyClassificationSystem</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
@@ -11315,7 +11354,7 @@
           <t>BuildingEnergyCodeSystem</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11339,9 +11378,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
@@ -11363,9 +11402,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
@@ -11387,9 +11426,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
@@ -11411,9 +11450,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
@@ -11435,9 +11474,9 @@
           <t>PrimaryEnergySource</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
@@ -11459,7 +11498,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11483,9 +11522,9 @@
           <t>BuildingFacingDirection</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
@@ -11507,9 +11546,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
@@ -11531,9 +11570,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
@@ -11555,9 +11594,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
@@ -11579,9 +11618,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
@@ -11603,7 +11642,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -11627,7 +11666,7 @@
           <t>GrossFloorAreaStandard</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -11651,9 +11690,9 @@
           <t>FloorAreaInclusions</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
@@ -11675,7 +11714,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11699,7 +11738,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11723,9 +11762,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
@@ -11747,9 +11786,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
@@ -11771,9 +11810,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
@@ -11795,9 +11834,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
@@ -11819,9 +11858,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
@@ -11843,9 +11882,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
@@ -11867,9 +11906,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
@@ -11891,9 +11930,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
@@ -11915,9 +11954,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
@@ -11939,7 +11978,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr">
+      <c r="E88" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -11963,9 +12002,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
@@ -11987,9 +12026,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
@@ -12011,7 +12050,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12035,9 +12074,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
@@ -12059,9 +12098,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
@@ -12083,9 +12122,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
@@ -12107,9 +12146,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
@@ -12131,9 +12170,9 @@
           <t>ReplacementCountMethod</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
@@ -12155,9 +12194,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
@@ -12179,7 +12218,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -12203,7 +12242,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12227,7 +12266,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12251,9 +12290,9 @@
           <t>LCADatabase</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -12275,7 +12314,7 @@
           <t>LCADatabaseSystemModel</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E102" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -12299,9 +12338,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>Removed</t>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
@@ -12563,7 +12602,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr">
+      <c r="E114" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -12587,7 +12626,7 @@
           <t>LCATemporalApproach</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12611,7 +12650,7 @@
           <t>OnSiteRenewableAllocationApproach</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr">
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -12635,7 +12674,7 @@
           <t>SharedComponentAllocationRule</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12659,7 +12698,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12683,7 +12722,7 @@
           <t>ExtendedDefaultDataBasis</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12707,7 +12746,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12731,7 +12770,7 @@
           <t>LimitValueScopeReduction</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12755,7 +12794,7 @@
           <t>EmissionFactorScenario</t>
         </is>
       </c>
-      <c r="E122" s="9" t="inlineStr">
+      <c r="E122" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -12779,7 +12818,7 @@
           <t>LCIModelingApproach</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -12803,7 +12842,7 @@
           <t>LifeCycleSystemBoundary</t>
         </is>
       </c>
-      <c r="E124" s="8" t="inlineStr">
+      <c r="E124" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -12827,9 +12866,9 @@
           <t>LCIAMethodology</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr"/>
@@ -12851,7 +12890,7 @@
           <t>BiogenicCarbonAccounting</t>
         </is>
       </c>
-      <c r="E126" s="9" t="inlineStr">
+      <c r="E126" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -12875,7 +12914,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E127" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -12899,9 +12938,9 @@
           <t>MaterialQuantitiesSource</t>
         </is>
       </c>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr"/>
@@ -12923,9 +12962,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr"/>
@@ -12947,9 +12986,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E130" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr"/>
@@ -12971,9 +13010,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E131" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
@@ -12995,9 +13034,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E132" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
@@ -13019,9 +13058,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
@@ -13043,9 +13082,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E134" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
@@ -13067,9 +13106,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
@@ -13091,9 +13130,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
@@ -13115,9 +13154,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
@@ -13139,9 +13178,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E138" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
@@ -13163,9 +13202,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E139" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
@@ -13187,9 +13226,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E140" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
@@ -13211,9 +13250,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E141" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
@@ -13235,9 +13274,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
@@ -13259,9 +13298,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
@@ -13283,9 +13322,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E144" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
@@ -13307,9 +13346,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
@@ -13331,9 +13370,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E146" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
@@ -13355,9 +13394,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E147" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
@@ -13379,9 +13418,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
@@ -13403,9 +13442,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
@@ -13427,7 +13466,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13451,7 +13490,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13475,7 +13514,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13499,7 +13538,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13523,7 +13562,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13547,7 +13586,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13571,7 +13610,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E156" s="9" t="inlineStr">
+      <c r="E156" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13595,7 +13634,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E157" s="9" t="inlineStr">
+      <c r="E157" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13619,7 +13658,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E158" s="9" t="inlineStr">
+      <c r="E158" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13643,7 +13682,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E159" s="9" t="inlineStr">
+      <c r="E159" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13667,7 +13706,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E160" s="9" t="inlineStr">
+      <c r="E160" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13691,7 +13730,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E161" s="9" t="inlineStr">
+      <c r="E161" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13715,7 +13754,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13739,7 +13778,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13763,7 +13802,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13787,7 +13826,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13811,7 +13850,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E166" s="9" t="inlineStr">
+      <c r="E166" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13835,7 +13874,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13859,7 +13898,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -13883,7 +13922,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13907,7 +13946,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E170" s="9" t="inlineStr">
+      <c r="E170" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13931,7 +13970,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E171" s="9" t="inlineStr">
+      <c r="E171" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13955,7 +13994,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E172" s="9" t="inlineStr">
+      <c r="E172" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -13979,7 +14018,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E173" s="9" t="inlineStr">
+      <c r="E173" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14003,7 +14042,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14027,7 +14066,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14051,7 +14090,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14075,7 +14114,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E177" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14099,7 +14138,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E178" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14123,7 +14162,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14147,7 +14186,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14171,7 +14210,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14195,7 +14234,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14219,7 +14258,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14243,7 +14282,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -14267,7 +14306,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E185" s="9" t="inlineStr">
+      <c r="E185" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14291,7 +14330,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E186" s="9" t="inlineStr">
+      <c r="E186" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14315,7 +14354,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E187" s="9" t="inlineStr">
+      <c r="E187" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14339,7 +14378,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E188" s="9" t="inlineStr">
+      <c r="E188" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14363,7 +14402,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E189" s="9" t="inlineStr">
+      <c r="E189" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14387,7 +14426,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E190" s="9" t="inlineStr">
+      <c r="E190" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -14411,7 +14450,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E191" s="9" t="inlineStr">
+      <c r="E191" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -15699,9 +15738,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
@@ -15747,9 +15786,9 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
@@ -15771,9 +15810,9 @@
           <t>AboveBelowGround</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
@@ -15795,9 +15834,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
@@ -15819,9 +15858,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -15843,9 +15882,9 @@
           <t>OpenBDFBuildingElementClassification</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
@@ -15867,9 +15906,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -15891,7 +15930,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15915,7 +15954,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -15939,9 +15978,9 @@
           <t>OpenBDFMaterialClassification</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
@@ -15963,7 +16002,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -15987,9 +16026,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -16011,7 +16050,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -16035,7 +16074,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16107,9 +16146,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
@@ -16131,7 +16170,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16155,7 +16194,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -16179,9 +16218,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
@@ -16203,9 +16242,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
@@ -16227,9 +16266,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
@@ -16251,9 +16290,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
@@ -16275,9 +16314,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
@@ -16299,9 +16338,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -21415,7 +21454,7 @@
           <t>DeclaredUnit</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21511,9 +21550,9 @@
           <t>MaterialDataType</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
@@ -21535,9 +21574,9 @@
           <t>MaterialEPDMatch</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -21559,7 +21598,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21583,7 +21622,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21607,7 +21646,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21631,7 +21670,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21655,7 +21694,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21679,7 +21718,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21703,7 +21742,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21727,7 +21766,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21751,7 +21790,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21775,7 +21814,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21799,7 +21838,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21823,7 +21862,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -21847,7 +21886,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22000,6 +22039,42 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Value in your format</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>OpenBDF floor level</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Leave the floor level empty to take the number carried by the label</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22077,7 +22152,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -22101,9 +22176,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
@@ -22125,7 +22200,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22149,7 +22224,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22173,7 +22248,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22197,9 +22272,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
@@ -22221,9 +22296,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
@@ -22245,7 +22320,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22269,7 +22344,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22293,7 +22368,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22317,7 +22392,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22341,9 +22416,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -22365,7 +22440,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22389,7 +22464,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22413,9 +22488,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -22437,9 +22512,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
@@ -22461,9 +22536,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -22485,9 +22560,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -22509,9 +22584,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
@@ -22533,7 +22608,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22557,7 +22632,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22581,7 +22656,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22605,7 +22680,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22629,7 +22704,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22653,7 +22728,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22677,7 +22752,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22701,7 +22776,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22725,7 +22800,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22749,7 +22824,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22773,7 +22848,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -22797,9 +22872,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
@@ -22821,9 +22896,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
@@ -22845,9 +22920,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
@@ -22869,9 +22944,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
@@ -22893,9 +22968,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -22917,9 +22992,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
@@ -22941,9 +23016,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
@@ -22965,9 +23040,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -22989,9 +23064,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -23013,7 +23088,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23037,7 +23112,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23061,7 +23136,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23085,9 +23160,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
@@ -23109,9 +23184,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
@@ -23133,9 +23208,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
@@ -23157,9 +23232,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
@@ -23181,9 +23256,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
@@ -23205,9 +23280,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
@@ -23229,9 +23304,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
@@ -23253,9 +23328,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
@@ -23277,7 +23352,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23301,7 +23376,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23325,9 +23400,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
@@ -23349,9 +23424,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
@@ -23373,9 +23448,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
@@ -23397,9 +23472,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
@@ -23421,9 +23496,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
@@ -23445,9 +23520,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
@@ -23469,9 +23544,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
@@ -23493,9 +23568,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
@@ -23517,9 +23592,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
@@ -23541,7 +23616,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23565,7 +23640,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23589,7 +23664,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23613,9 +23688,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
@@ -23637,9 +23712,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
@@ -23661,9 +23736,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -23685,9 +23760,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
@@ -23709,9 +23784,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
@@ -23733,9 +23808,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
@@ -23757,9 +23832,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
@@ -23781,9 +23856,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
@@ -23805,7 +23880,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23829,7 +23904,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -23853,9 +23928,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
@@ -23877,9 +23952,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
@@ -23901,9 +23976,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
@@ -23925,9 +24000,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
@@ -23949,9 +24024,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
@@ -23973,9 +24048,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
@@ -23997,9 +24072,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
@@ -24021,9 +24096,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
@@ -24045,9 +24120,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
@@ -24069,7 +24144,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24093,7 +24168,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24117,7 +24192,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24141,9 +24216,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
@@ -24165,9 +24240,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
@@ -24189,9 +24264,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
@@ -24213,9 +24288,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
@@ -24237,9 +24312,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
@@ -24261,9 +24336,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
@@ -24285,9 +24360,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
@@ -24309,9 +24384,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
@@ -24333,7 +24408,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24357,7 +24432,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24381,9 +24456,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
@@ -24405,9 +24480,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
@@ -24429,9 +24504,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
@@ -24453,9 +24528,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -24477,9 +24552,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
@@ -24501,9 +24576,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
@@ -24525,9 +24600,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
@@ -24549,9 +24624,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
@@ -24573,7 +24648,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24597,7 +24672,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24621,7 +24696,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24645,7 +24720,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24669,7 +24744,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24693,7 +24768,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24717,7 +24792,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24741,7 +24816,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24765,7 +24840,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24789,7 +24864,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24813,7 +24888,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24837,7 +24912,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24861,7 +24936,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24885,7 +24960,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24909,7 +24984,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24933,7 +25008,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24957,7 +25032,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -24981,7 +25056,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25005,7 +25080,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25029,7 +25104,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25053,7 +25128,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25077,7 +25152,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25101,7 +25176,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25125,7 +25200,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25149,7 +25224,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25173,7 +25248,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25197,7 +25272,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25221,7 +25296,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E133" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25245,7 +25320,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25269,7 +25344,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25293,7 +25368,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25317,7 +25392,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25341,7 +25416,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25365,7 +25440,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E139" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25389,7 +25464,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25413,7 +25488,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25437,7 +25512,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25461,7 +25536,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25485,7 +25560,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25509,7 +25584,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25533,7 +25608,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25557,7 +25632,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25581,7 +25656,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25605,7 +25680,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25629,7 +25704,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25653,7 +25728,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25677,7 +25752,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25701,7 +25776,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25725,7 +25800,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25749,7 +25824,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25773,7 +25848,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25797,7 +25872,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25821,7 +25896,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25845,7 +25920,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25869,7 +25944,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25893,7 +25968,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25917,7 +25992,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25941,7 +26016,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25965,7 +26040,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -25989,7 +26064,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26013,7 +26088,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E166" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26037,7 +26112,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26061,7 +26136,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26085,7 +26160,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26109,7 +26184,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26133,7 +26208,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26157,7 +26232,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26181,7 +26256,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26205,7 +26280,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26229,7 +26304,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26253,7 +26328,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26277,7 +26352,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26301,7 +26376,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E178" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26325,7 +26400,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26349,7 +26424,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26373,7 +26448,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26397,7 +26472,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26421,7 +26496,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26445,7 +26520,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26469,7 +26544,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26493,7 +26568,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26517,7 +26592,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26541,7 +26616,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26565,7 +26640,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26589,7 +26664,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26613,7 +26688,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26637,7 +26712,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26661,7 +26736,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26685,7 +26760,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E194" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26709,7 +26784,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26733,7 +26808,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26757,7 +26832,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26781,7 +26856,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26805,7 +26880,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26829,7 +26904,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26853,7 +26928,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26877,7 +26952,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="E202" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26901,7 +26976,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26925,7 +27000,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26949,7 +27024,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E205" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26973,7 +27048,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -26997,7 +27072,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27021,7 +27096,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27045,7 +27120,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27069,7 +27144,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27093,7 +27168,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="E211" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27117,7 +27192,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27141,7 +27216,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27165,7 +27240,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27189,7 +27264,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27213,7 +27288,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27237,7 +27312,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27261,7 +27336,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27285,7 +27360,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27309,7 +27384,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27333,7 +27408,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27357,7 +27432,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="E222" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27381,7 +27456,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="E223" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27405,7 +27480,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E224" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27429,7 +27504,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E225" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27453,7 +27528,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27477,7 +27552,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="E227" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27501,7 +27576,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27525,7 +27600,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27549,7 +27624,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27573,7 +27648,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27597,7 +27672,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E232" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27621,7 +27696,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E233" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27645,7 +27720,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="E234" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27669,7 +27744,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="E235" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27693,7 +27768,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27717,7 +27792,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27741,7 +27816,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="E238" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27765,7 +27840,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27789,7 +27864,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27813,7 +27888,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27837,7 +27912,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27861,7 +27936,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27885,7 +27960,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27909,7 +27984,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E245" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27933,7 +28008,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27957,7 +28032,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E247" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -27981,7 +28056,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28005,7 +28080,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E249" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28029,7 +28104,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E250" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28053,7 +28128,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E251" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28077,7 +28152,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E252" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28101,7 +28176,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="E253" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28125,7 +28200,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="E254" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28149,7 +28224,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="E255" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28173,7 +28248,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="E256" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28197,7 +28272,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="E257" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28221,7 +28296,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="E258" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28245,7 +28320,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="E259" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28269,7 +28344,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="E260" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28293,7 +28368,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E261" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28317,7 +28392,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="E262" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28341,7 +28416,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E263" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28365,7 +28440,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="E264" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28389,7 +28464,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="E265" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28413,7 +28488,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28437,7 +28512,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28461,7 +28536,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28485,7 +28560,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28509,7 +28584,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28533,7 +28608,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28557,7 +28632,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="E272" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28581,7 +28656,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="E273" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28605,7 +28680,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="E274" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28629,7 +28704,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="E275" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28653,7 +28728,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28677,7 +28752,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="E277" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28701,7 +28776,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="E278" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28725,7 +28800,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="E279" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28749,7 +28824,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="E280" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28773,7 +28848,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="E281" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28797,7 +28872,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="E282" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28821,7 +28896,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="E283" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28845,7 +28920,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="E284" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28869,7 +28944,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="E285" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28893,7 +28968,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="E286" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28917,7 +28992,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="E287" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28941,7 +29016,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="E288" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28965,7 +29040,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="E289" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -28989,7 +29064,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="E290" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29013,7 +29088,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29037,7 +29112,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="E292" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29061,7 +29136,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29085,7 +29160,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29109,7 +29184,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29133,7 +29208,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29157,7 +29232,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29181,7 +29256,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29205,7 +29280,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E299" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29229,7 +29304,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29253,7 +29328,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="E301" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29277,7 +29352,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="E302" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29301,7 +29376,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="E303" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29325,7 +29400,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="E304" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29349,7 +29424,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="E305" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29373,7 +29448,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="E306" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29397,7 +29472,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="E307" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29421,7 +29496,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="E308" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29445,7 +29520,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29469,7 +29544,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="E310" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29493,7 +29568,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="E311" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29517,7 +29592,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="E312" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29541,7 +29616,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="E313" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29565,7 +29640,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="E314" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29589,7 +29664,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="E315" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29613,7 +29688,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29637,7 +29712,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29661,7 +29736,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29685,7 +29760,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29709,7 +29784,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29733,7 +29808,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29757,7 +29832,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29781,7 +29856,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29805,7 +29880,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29829,7 +29904,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29853,7 +29928,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="E326" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29877,7 +29952,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="E327" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29901,7 +29976,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="E328" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29925,7 +30000,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="E329" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29949,7 +30024,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="E330" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29973,7 +30048,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="E331" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -29997,7 +30072,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="E332" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30021,7 +30096,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="E333" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30045,7 +30120,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="E334" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30069,7 +30144,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="E335" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30093,7 +30168,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="E336" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30117,7 +30192,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="E337" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30141,7 +30216,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="E338" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30165,7 +30240,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="E339" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30189,7 +30264,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="E340" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30213,7 +30288,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="E341" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30237,7 +30312,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="E342" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30261,7 +30336,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="E343" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30285,7 +30360,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="E344" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30309,7 +30384,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="E345" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30333,7 +30408,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="E346" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30357,7 +30432,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="E347" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30381,7 +30456,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="E348" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30405,7 +30480,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="E349" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30429,7 +30504,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="E350" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30453,7 +30528,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="E351" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30477,7 +30552,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="E352" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30501,7 +30576,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="E353" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30525,7 +30600,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="E354" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30549,7 +30624,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="E355" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30573,7 +30648,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="E356" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30597,7 +30672,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="E357" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30621,7 +30696,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="E358" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30645,7 +30720,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="E359" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30669,7 +30744,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="E360" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30693,7 +30768,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="E361" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30717,7 +30792,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="E362" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30741,7 +30816,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="E363" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30765,7 +30840,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="E364" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30789,7 +30864,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="E365" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30813,7 +30888,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="E366" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30837,7 +30912,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="E367" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30861,7 +30936,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="E368" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30885,7 +30960,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="E369" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30909,7 +30984,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="E370" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30933,7 +31008,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="E371" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30957,7 +31032,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="E372" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -30981,7 +31056,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="E373" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31005,7 +31080,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="E374" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31029,7 +31104,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="E375" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31053,7 +31128,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="E376" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31077,7 +31152,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="E377" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31101,7 +31176,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="E378" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31125,7 +31200,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="E379" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31149,7 +31224,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="E380" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31173,7 +31248,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="E381" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31197,7 +31272,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="E382" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31221,7 +31296,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="E383" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31245,7 +31320,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="E384" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31269,7 +31344,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="E385" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31293,7 +31368,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="E386" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31317,7 +31392,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="E387" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31341,7 +31416,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="E388" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31365,7 +31440,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="E389" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31389,7 +31464,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="E390" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31413,7 +31488,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="E391" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31437,7 +31512,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="E392" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31461,7 +31536,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="E393" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31485,7 +31560,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="E394" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31509,7 +31584,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="E395" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31533,7 +31608,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="E396" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31557,7 +31632,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="E397" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31581,7 +31656,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="E398" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31605,7 +31680,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="E399" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31629,7 +31704,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="E400" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31653,7 +31728,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="E401" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31677,7 +31752,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="E402" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31701,7 +31776,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="E403" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31725,7 +31800,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="E404" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31749,7 +31824,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="E405" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31773,7 +31848,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="E406" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31797,7 +31872,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="E407" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31821,7 +31896,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="E408" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31845,7 +31920,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="E409" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31869,7 +31944,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="E410" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31893,7 +31968,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="E411" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31917,7 +31992,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="E412" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31941,7 +32016,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="E413" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31965,7 +32040,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="E414" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -31989,7 +32064,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="E415" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32013,7 +32088,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="E416" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32037,7 +32112,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="E417" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32061,7 +32136,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="E418" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32085,7 +32160,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="E419" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32109,7 +32184,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="E420" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32133,7 +32208,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="E421" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32157,7 +32232,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="E422" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32181,7 +32256,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="E423" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32205,7 +32280,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="E424" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32229,7 +32304,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="E425" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32253,7 +32328,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="E426" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32277,7 +32352,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="E427" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32301,7 +32376,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="E428" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32325,7 +32400,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="E429" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32349,7 +32424,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="E430" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32373,7 +32448,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="E431" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32397,7 +32472,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="E432" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32421,7 +32496,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="E433" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32445,7 +32520,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="E434" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32469,7 +32544,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="E435" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32493,7 +32568,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="E436" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32517,7 +32592,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="E437" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32541,7 +32616,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="E438" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32565,7 +32640,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="E439" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32589,7 +32664,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="E440" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32613,7 +32688,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="E441" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32637,7 +32712,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="E442" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32661,7 +32736,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="E443" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32685,7 +32760,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="E444" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32709,7 +32784,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="E445" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32733,7 +32808,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="E446" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32757,7 +32832,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="E447" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32781,7 +32856,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="E448" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32805,7 +32880,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="E449" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32829,7 +32904,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="E450" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32853,7 +32928,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="E451" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32877,7 +32952,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="E452" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32901,7 +32976,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="E453" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32925,7 +33000,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="E454" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32949,7 +33024,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="E455" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32973,7 +33048,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="E456" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -32997,7 +33072,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="E457" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33021,7 +33096,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="E458" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33045,7 +33120,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="E459" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33069,7 +33144,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="E460" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33093,7 +33168,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="E461" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33117,7 +33192,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="E462" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33141,7 +33216,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="E463" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33165,7 +33240,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="E464" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33189,7 +33264,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="E465" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33213,7 +33288,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="E466" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33237,7 +33312,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="E467" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33261,7 +33336,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="E468" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33285,7 +33360,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="E469" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33309,7 +33384,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="E470" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33333,7 +33408,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="E471" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33357,7 +33432,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="E472" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33381,7 +33456,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="E473" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33405,7 +33480,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="E474" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33429,7 +33504,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="E475" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33453,7 +33528,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="E476" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33477,7 +33552,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="E477" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33501,7 +33576,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="E478" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33525,7 +33600,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="E479" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33549,7 +33624,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="E480" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33573,7 +33648,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="E481" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33597,7 +33672,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="E482" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33621,7 +33696,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="E483" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33645,7 +33720,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="E484" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33669,7 +33744,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="E485" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33693,7 +33768,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="E486" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33717,7 +33792,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="E487" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33741,7 +33816,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="E488" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33765,7 +33840,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="E489" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33789,7 +33864,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="E490" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33813,7 +33888,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="E491" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33837,7 +33912,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="E492" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33861,7 +33936,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="E493" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33885,7 +33960,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="E494" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33909,7 +33984,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="E495" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33933,7 +34008,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="E496" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33957,7 +34032,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="E497" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -33981,7 +34056,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="E498" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34005,7 +34080,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="E499" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34029,7 +34104,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="E500" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34053,7 +34128,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="E501" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34077,7 +34152,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="E502" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34101,7 +34176,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="E503" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34125,7 +34200,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="E504" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34149,7 +34224,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="E505" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34173,7 +34248,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="E506" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34197,7 +34272,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="E507" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34221,7 +34296,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="E508" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34245,7 +34320,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="E509" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34269,7 +34344,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="E510" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34293,7 +34368,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="E511" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34317,7 +34392,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="E512" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34341,7 +34416,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="E513" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34365,7 +34440,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="E514" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34389,7 +34464,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="E515" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34413,7 +34488,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="E516" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34437,7 +34512,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="E517" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34461,7 +34536,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="E518" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34485,7 +34560,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="E519" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34509,7 +34584,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="E520" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34533,7 +34608,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="E521" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34557,7 +34632,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="E522" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34581,7 +34656,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="E523" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34605,7 +34680,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="E524" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34629,7 +34704,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="E525" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34653,7 +34728,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="E526" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34677,7 +34752,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="E527" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34701,7 +34776,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E528" s="6" t="inlineStr">
+      <c r="E528" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34725,7 +34800,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E529" s="6" t="inlineStr">
+      <c r="E529" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34749,7 +34824,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E530" s="6" t="inlineStr">
+      <c r="E530" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34773,7 +34848,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E531" s="6" t="inlineStr">
+      <c r="E531" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34797,7 +34872,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E532" s="6" t="inlineStr">
+      <c r="E532" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34821,7 +34896,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E533" s="6" t="inlineStr">
+      <c r="E533" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34845,7 +34920,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E534" s="6" t="inlineStr">
+      <c r="E534" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34869,7 +34944,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E535" s="6" t="inlineStr">
+      <c r="E535" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34893,7 +34968,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E536" s="6" t="inlineStr">
+      <c r="E536" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34917,7 +34992,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E537" s="6" t="inlineStr">
+      <c r="E537" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34941,7 +35016,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E538" s="6" t="inlineStr">
+      <c r="E538" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34965,7 +35040,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E539" s="6" t="inlineStr">
+      <c r="E539" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -34989,7 +35064,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E540" s="6" t="inlineStr">
+      <c r="E540" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35013,7 +35088,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E541" s="6" t="inlineStr">
+      <c r="E541" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35037,7 +35112,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E542" s="6" t="inlineStr">
+      <c r="E542" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35061,7 +35136,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E543" s="6" t="inlineStr">
+      <c r="E543" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35085,7 +35160,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E544" s="6" t="inlineStr">
+      <c r="E544" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35109,7 +35184,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E545" s="6" t="inlineStr">
+      <c r="E545" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35133,7 +35208,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E546" s="6" t="inlineStr">
+      <c r="E546" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35157,7 +35232,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E547" s="6" t="inlineStr">
+      <c r="E547" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35181,7 +35256,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E548" s="6" t="inlineStr">
+      <c r="E548" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35205,7 +35280,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E549" s="6" t="inlineStr">
+      <c r="E549" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35229,7 +35304,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E550" s="6" t="inlineStr">
+      <c r="E550" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35253,7 +35328,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E551" s="6" t="inlineStr">
+      <c r="E551" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35277,7 +35352,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E552" s="6" t="inlineStr">
+      <c r="E552" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35301,7 +35376,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E553" s="6" t="inlineStr">
+      <c r="E553" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35325,7 +35400,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E554" s="6" t="inlineStr">
+      <c r="E554" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35349,7 +35424,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E555" s="6" t="inlineStr">
+      <c r="E555" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35373,7 +35448,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="E556" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35397,7 +35472,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E557" s="6" t="inlineStr">
+      <c r="E557" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35421,7 +35496,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E558" s="6" t="inlineStr">
+      <c r="E558" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35445,7 +35520,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E559" s="6" t="inlineStr">
+      <c r="E559" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35469,7 +35544,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E560" s="6" t="inlineStr">
+      <c r="E560" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35493,7 +35568,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E561" s="6" t="inlineStr">
+      <c r="E561" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35517,7 +35592,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E562" s="6" t="inlineStr">
+      <c r="E562" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35541,7 +35616,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E563" s="6" t="inlineStr">
+      <c r="E563" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35565,7 +35640,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E564" s="6" t="inlineStr">
+      <c r="E564" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35589,7 +35664,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E565" s="6" t="inlineStr">
+      <c r="E565" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35613,7 +35688,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E566" s="6" t="inlineStr">
+      <c r="E566" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35637,7 +35712,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="E567" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35661,7 +35736,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E568" s="6" t="inlineStr">
+      <c r="E568" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35685,7 +35760,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E569" s="6" t="inlineStr">
+      <c r="E569" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35709,7 +35784,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E570" s="6" t="inlineStr">
+      <c r="E570" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35733,7 +35808,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E571" s="6" t="inlineStr">
+      <c r="E571" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35757,7 +35832,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E572" s="6" t="inlineStr">
+      <c r="E572" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35781,7 +35856,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E573" s="6" t="inlineStr">
+      <c r="E573" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35805,7 +35880,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E574" s="6" t="inlineStr">
+      <c r="E574" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35829,7 +35904,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E575" s="6" t="inlineStr">
+      <c r="E575" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35853,7 +35928,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E576" s="6" t="inlineStr">
+      <c r="E576" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35877,7 +35952,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E577" s="6" t="inlineStr">
+      <c r="E577" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35901,7 +35976,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E578" s="6" t="inlineStr">
+      <c r="E578" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35925,7 +36000,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E579" s="6" t="inlineStr">
+      <c r="E579" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35949,7 +36024,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E580" s="6" t="inlineStr">
+      <c r="E580" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35973,7 +36048,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E581" s="6" t="inlineStr">
+      <c r="E581" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -35997,7 +36072,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E582" s="6" t="inlineStr">
+      <c r="E582" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36021,7 +36096,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E583" s="6" t="inlineStr">
+      <c r="E583" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36045,7 +36120,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E584" s="6" t="inlineStr">
+      <c r="E584" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36069,7 +36144,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E585" s="6" t="inlineStr">
+      <c r="E585" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36093,7 +36168,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E586" s="6" t="inlineStr">
+      <c r="E586" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36117,7 +36192,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E587" s="6" t="inlineStr">
+      <c r="E587" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36141,7 +36216,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E588" s="6" t="inlineStr">
+      <c r="E588" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36165,7 +36240,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E589" s="6" t="inlineStr">
+      <c r="E589" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36189,7 +36264,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E590" s="6" t="inlineStr">
+      <c r="E590" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36213,7 +36288,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E591" s="6" t="inlineStr">
+      <c r="E591" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36237,7 +36312,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E592" s="6" t="inlineStr">
+      <c r="E592" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36261,7 +36336,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E593" s="6" t="inlineStr">
+      <c r="E593" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36285,7 +36360,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E594" s="6" t="inlineStr">
+      <c r="E594" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36309,7 +36384,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E595" s="6" t="inlineStr">
+      <c r="E595" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36333,7 +36408,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E596" s="6" t="inlineStr">
+      <c r="E596" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36357,7 +36432,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E597" s="6" t="inlineStr">
+      <c r="E597" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36381,7 +36456,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E598" s="6" t="inlineStr">
+      <c r="E598" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36405,7 +36480,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E599" s="6" t="inlineStr">
+      <c r="E599" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36429,7 +36504,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E600" s="6" t="inlineStr">
+      <c r="E600" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36453,7 +36528,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E601" s="6" t="inlineStr">
+      <c r="E601" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36477,7 +36552,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E602" s="6" t="inlineStr">
+      <c r="E602" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36501,7 +36576,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E603" s="6" t="inlineStr">
+      <c r="E603" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36525,7 +36600,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E604" s="6" t="inlineStr">
+      <c r="E604" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36549,7 +36624,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E605" s="6" t="inlineStr">
+      <c r="E605" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36573,7 +36648,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E606" s="6" t="inlineStr">
+      <c r="E606" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36597,7 +36672,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E607" s="6" t="inlineStr">
+      <c r="E607" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36621,7 +36696,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E608" s="6" t="inlineStr">
+      <c r="E608" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36645,7 +36720,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E609" s="6" t="inlineStr">
+      <c r="E609" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36669,7 +36744,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E610" s="6" t="inlineStr">
+      <c r="E610" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36693,7 +36768,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E611" s="6" t="inlineStr">
+      <c r="E611" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -36777,7 +36852,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -36801,7 +36876,7 @@
           <t>LCAStageOrModuleOrSubModule</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -36897,9 +36972,9 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
@@ -36921,9 +36996,9 @@
           <t>MaterialFlowType</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
@@ -36945,9 +37020,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -36969,9 +37044,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
@@ -36993,9 +37068,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -37017,9 +37092,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
@@ -37041,9 +37116,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -37065,9 +37140,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
@@ -37089,7 +37164,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37113,7 +37188,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37137,7 +37212,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37161,7 +37236,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37185,7 +37260,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37209,7 +37284,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37233,7 +37308,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37257,7 +37332,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37281,7 +37356,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37305,7 +37380,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37329,7 +37404,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37353,7 +37428,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37377,7 +37452,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37401,7 +37476,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37425,7 +37500,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37449,7 +37524,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37473,7 +37548,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37497,7 +37572,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37521,7 +37596,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37545,7 +37620,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37569,7 +37644,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37593,7 +37668,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -37617,7 +37692,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>

--- a/translators/templates/translator_template_v2.0.0.xlsx
+++ b/translators/templates/translator_template_v2.0.0.xlsx
@@ -24166,12 +24166,12 @@
       <c r="A39" s="5" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>gwp_total_total</t>
+          <t>gwp_total</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Total Global Warming Potential - Total</t>
+          <t>Total Global Warming Potential</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">

--- a/translators/templates/translator_template_v2.0.0.xlsx
+++ b/translators/templates/translator_template_v2.0.0.xlsx
@@ -127,7 +127,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003592e3"/>
+        <fgColor rgb="0072b7ed"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,12 +137,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0031658d"/>
+        <fgColor rgb="003592e3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009dd2f3"/>
+        <fgColor rgb="00b8e0f7"/>
       </patternFill>
     </fill>
     <fill>
@@ -190,10 +190,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1"/>
@@ -219,10 +219,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="9"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="6"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="8"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="5"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10669,9 +10669,9 @@
           <t>Country</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>

--- a/translators/templates/translator_template_v2.0.0.xlsx
+++ b/translators/templates/translator_template_v2.0.0.xlsx
@@ -784,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -880,6 +880,21 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5371,7 +5386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5468,6 +5483,21 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5479,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5723,6 +5753,21 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15496,7 +15541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15608,6 +15653,21 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17318,7 +17378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -17449,6 +17509,21 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/translators/templates/translator_template_v2.0.0.xlsx
+++ b/translators/templates/translator_template_v2.0.0.xlsx
@@ -4690,7 +4690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5151,12 +5151,12 @@
       <c r="A30" s="5" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>GBDI_EndOfUse</t>
+          <t>LMVM_AT_LPH1_Grundlagenanalyse</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>GBDI_EndOfUse</t>
+          <t>LMVM_AT_LPH1_Grundlagenanalyse</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -5166,16 +5166,526 @@
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Other_National</t>
+          <t>LMVM_AT_LPH2_Vorentwurf</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Other_National</t>
+          <t>LMVM_AT_LPH2_Vorentwurf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH3_Entwurfsplanung</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH3_Entwurfsplanung</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH4_Einreichplanung</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH4_Einreichplanung</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH5_Ausfuehrungsplanung</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH5_Ausfuehrungsplanung</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH6_Ausschreibung</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH6_Ausschreibung</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH7_BegleitungBauausfuehrung</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH7_BegleitungBauausfuehrung</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH8_OertlicheBauaufsichtDokumentation</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH8_OertlicheBauaufsichtDokumentation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH9_Objektbetreuung</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>LMVM_AT_LPH9_Objektbetreuung</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_ESQ_Esquisse</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_ESQ_Esquisse</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_DIAG_Diagnostic</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_DIAG_Diagnostic</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_APS_AvantProjetSommaire</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_APS_AvantProjetSommaire</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_APD_AvantProjetDefinitif</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_APD_AvantProjetDefinitif</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr"/>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_PRO_EtudesProjet</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_PRO_EtudesProjet</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_ACT_AssistanceContratsTravaux</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_ACT_AssistanceContratsTravaux</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_EXE_EtudesExecution</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_EXE_EtudesExecution</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_VISA_VisaEtudesExecution</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_VISA_VisaEtudesExecution</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_DET_DirectionExecutionTravaux</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_DET_DirectionExecutionTravaux</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>MOP_FR_AOR_AssistanceOperationsReception</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>MOP_FR_AOR_AssistanceOperationsReception</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr"/>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_1_InitiatiefHaalbaarheid</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_1_InitiatiefHaalbaarheid</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_2_Projectdefinitie</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_2_Projectdefinitie</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr"/>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_3_Structuurontwerp</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_3_Structuurontwerp</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr"/>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_4_Voorontwerp</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_4_Voorontwerp</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr"/>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_5_DefinitiefOntwerp</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_5_DefinitiefOntwerp</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_6_TechnischOntwerpBestek</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_6_TechnischOntwerpBestek</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_7_PrijsEnContractvorming</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_7_PrijsEnContractvorming</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_8_UitvoeringsgereedOntwerp</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_8_UitvoeringsgereedOntwerp</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr"/>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_9_Directievoering</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_9_Directievoering</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_10_GebruikExploitatie</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>DNRSTB_NL_10_GebruikExploitatie</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>LOE_ES_EP_EstudiosPrevios</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>LOE_ES_EP_EstudiosPrevios</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>LOE_ES_AP_Anteproyecto</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>LOE_ES_AP_Anteproyecto</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>LOE_ES_PB_ProyectoBasico</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>LOE_ES_PB_ProyectoBasico</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>LOE_ES_PE_ProyectoEjecucion</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>LOE_ES_PE_ProyectoEjecucion</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>LOE_ES_DO_DireccionObra</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>LOE_ES_DO_DireccionObra</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>GBDI_EndOfUse</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>GBDI_EndOfUse</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Other_National</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Other_National</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5349,12 +5859,12 @@
       <c r="A10" s="5" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>8 End of use, re-cycling</t>
+          <t>8 End of use, recycling</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>8 End of use, re-cycling</t>
+          <t>8 End of use, recycling</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>

--- a/translators/templates/translator_template_v2.0.0.xlsx
+++ b/translators/templates/translator_template_v2.0.0.xlsx
@@ -35,29 +35,28 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PrimaryEnergySource" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingFacingDirection" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GrossFloorAreaStandard" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FloorAreaInclusions" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReplacementCountMethod" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCADatabase" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCADatabaseSystemModel" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataWeightingBasis" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCATemporalApproach" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OnSiteRenewableAllocationApproach" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SharedComponentAllocationRule" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtendedDefaultDataBasis" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LimitValueScopeReduction" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EmissionFactorScenario" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCIModelingApproach" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LifeCycleSystemBoundary" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCIAMethodology" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BiogenicCarbonAccounting" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialQuantitiesSource" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AboveBelowGround" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenBDFBuildingElementClassification" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenBDFMaterialClassification" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialDataType" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialEPDMatch" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeclaredUnit" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FloorLevel" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReplacementCountMethod" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCADatabase" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCADatabaseSystemModel" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataWeightingBasis" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCATemporalApproach" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OnSiteRenewableAllocationApproach" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SharedComponentAllocationRule" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtendedDefaultDataBasis" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LimitValueScopeReduction" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EmissionFactorScenario" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCIModelingApproach" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LifeCycleSystemBoundary" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCIAMethodology" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BiogenicCarbonAccounting" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialQuantitiesSource" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AboveBelowGround" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenBDFBuildingElementClassification" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenBDFMaterialClassification" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialDataType" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaterialEPDMatch" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeclaredUnit" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FloorLevel" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10822,7 +10821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10863,17 +10862,17 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>enclosed_parking</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Enclosed parking (shares structure, inside envelope)</t>
+          <t>Integer (whole replacements only)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>shares structure, inside envelope</t>
+          <t>whole replacements only</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -10882,17 +10881,17 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>detached_parking</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Detached parking (structurally independent)</t>
+          <t>Decimal (fractional replacements allowed)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>structurally independent</t>
+          <t>fractional replacements allowed</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -10901,76 +10900,20 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>unconditioned_space</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Unconditioned space</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Unknown (rule not declared)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rule not declared</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>circulation</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Circulation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>technical_space</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Technical space</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>ancillary_external_buildings</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Ancillary external buildings</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>none_of_the_above</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>None of the above</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10983,7 +10926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11874,9 +11817,9 @@
           <t>GFAMeasurementMethod</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
@@ -12886,17 +12829,17 @@
       <c r="A76" s="5" t="inlineStr"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>building_floor_area_inclusions</t>
+          <t>floor_area_includes_enclosed_parking</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Floor area spatial inclusions</t>
+          <t>Floor area includes enclosed parking</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>FloorAreaInclusions</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -12911,22 +12854,22 @@
       <c r="A77" s="5" t="inlineStr"/>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>building_circulation_area</t>
+          <t>floor_area_includes_detached_parking</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Circulation area</t>
+          <t>Floor area includes detached parking</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
@@ -12936,22 +12879,22 @@
       <c r="A78" s="5" t="inlineStr"/>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>building_technical_area</t>
+          <t>floor_area_includes_unconditioned_space</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Technical area</t>
+          <t>Floor area includes unconditioned space</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
@@ -12961,22 +12904,22 @@
       <c r="A79" s="5" t="inlineStr"/>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>building_built_floor_area</t>
+          <t>floor_area_includes_circulation</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Built floor area (BFA)</t>
+          <t>Floor area includes circulation</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
@@ -12986,22 +12929,22 @@
       <c r="A80" s="5" t="inlineStr"/>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>building_envelope_area</t>
+          <t>floor_area_includes_technical_space</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Thermal envelope area</t>
+          <t>Floor area includes technical space</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E80" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
@@ -13011,22 +12954,22 @@
       <c r="A81" s="5" t="inlineStr"/>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>building_window_area</t>
+          <t>floor_area_includes_ancillary_external_buildings</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Window area</t>
+          <t>Floor area includes ancillary external buildings</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
@@ -13036,12 +12979,12 @@
       <c r="A82" s="5" t="inlineStr"/>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>building_wall_area_interior</t>
+          <t>building_circulation_area</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Wall area (interior)</t>
+          <t>Circulation area</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -13049,9 +12992,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
@@ -13061,12 +13004,12 @@
       <c r="A83" s="5" t="inlineStr"/>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>building_enclosed_parking_area</t>
+          <t>building_technical_area</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Enclosed parking area</t>
+          <t>Technical area</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -13074,9 +13017,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
@@ -13086,12 +13029,12 @@
       <c r="A84" s="5" t="inlineStr"/>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>building_height</t>
+          <t>building_built_floor_area</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Building height</t>
+          <t>Built floor area (BFA)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -13111,12 +13054,12 @@
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>building_floor_height</t>
+          <t>building_envelope_area</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Average floor height</t>
+          <t>Thermal envelope area</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -13136,12 +13079,12 @@
       <c r="A86" s="5" t="inlineStr"/>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>building_volume</t>
+          <t>building_window_area</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Building volume</t>
+          <t>Window area</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -13161,12 +13104,12 @@
       <c r="A87" s="5" t="inlineStr"/>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>building_occupancy_count</t>
+          <t>building_wall_area_interior</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Occupancy count</t>
+          <t>Wall area (interior)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -13186,22 +13129,22 @@
       <c r="A88" s="5" t="inlineStr"/>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>lca_assessment_date</t>
+          <t>building_enclosed_parking_area</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Project date of assessment</t>
+          <t>Enclosed parking area</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
@@ -13211,17 +13154,17 @@
       <c r="A89" s="5" t="inlineStr"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>lca_third_party_verified</t>
+          <t>building_height</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Third party verified</t>
+          <t>Building height</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
@@ -13236,17 +13179,17 @@
       <c r="A90" s="5" t="inlineStr"/>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>lca_third_party_verifier_name</t>
+          <t>building_floor_height</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Third party verifier name</t>
+          <t>Average floor height</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -13261,22 +13204,22 @@
       <c r="A91" s="5" t="inlineStr"/>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>lca_verification_date</t>
+          <t>building_volume</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Verification date</t>
+          <t>Building volume</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
@@ -13286,22 +13229,22 @@
       <c r="A92" s="5" t="inlineStr"/>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>lca_building_regulation_code</t>
+          <t>building_occupancy_count</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Building regulation/code</t>
+          <t>Occupancy count</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
@@ -13311,22 +13254,22 @@
       <c r="A93" s="5" t="inlineStr"/>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>lca_goal</t>
+          <t>lca_assessment_date</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>LCA goal</t>
+          <t>Project date of assessment</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
@@ -13336,22 +13279,22 @@
       <c r="A94" s="5" t="inlineStr"/>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>lca_reference_unit</t>
+          <t>lca_third_party_verified</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Reference Unit</t>
+          <t>Third party verified</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
@@ -13361,12 +13304,12 @@
       <c r="A95" s="5" t="inlineStr"/>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>lca_reference_study_period</t>
+          <t>lca_third_party_verifier_name</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Reference Study Period (RSP)</t>
+          <t>Third party verifier name</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -13374,9 +13317,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
@@ -13386,22 +13329,22 @@
       <c r="A96" s="5" t="inlineStr"/>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>lca_replacement_count_method</t>
+          <t>lca_verification_date</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Replacement count method</t>
+          <t>Verification date</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>ReplacementCountMethod</t>
-        </is>
-      </c>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
@@ -13411,12 +13354,12 @@
       <c r="A97" s="5" t="inlineStr"/>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>lca_functional_unit</t>
+          <t>lca_building_regulation_code</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Functional unit</t>
+          <t>Building regulation/code</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -13436,12 +13379,12 @@
       <c r="A98" s="5" t="inlineStr"/>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>lca_software_name</t>
+          <t>lca_goal</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>LCA Software name</t>
+          <t>LCA goal</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -13449,9 +13392,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
@@ -13461,12 +13404,12 @@
       <c r="A99" s="5" t="inlineStr"/>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>lca_software_publisher</t>
+          <t>lca_reference_unit</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>LCA software publisher</t>
+          <t>Reference Unit</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -13474,9 +13417,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
@@ -13486,12 +13429,12 @@
       <c r="A100" s="5" t="inlineStr"/>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>lca_software_version</t>
+          <t>lca_reference_study_period</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>LCA software version</t>
+          <t>Reference Study Period (RSP)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -13499,9 +13442,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
@@ -13511,17 +13454,17 @@
       <c r="A101" s="5" t="inlineStr"/>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>lca_database_name</t>
+          <t>lca_replacement_count_method</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>LCA database name</t>
+          <t>Replacement count method</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>LCADatabase</t>
+          <t>ReplacementCountMethod</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -13536,22 +13479,22 @@
       <c r="A102" s="5" t="inlineStr"/>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>lca_database_system_model</t>
+          <t>lca_functional_unit</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Database system model</t>
+          <t>Functional unit</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>LCADatabaseSystemModel</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>Required</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
@@ -13561,12 +13504,12 @@
       <c r="A103" s="5" t="inlineStr"/>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>lca_database_version</t>
+          <t>lca_software_name</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>LCA database version</t>
+          <t>LCA Software name</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -13574,9 +13517,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
@@ -13586,22 +13529,22 @@
       <c r="A104" s="5" t="inlineStr"/>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>lca_data_cpr_share</t>
+          <t>lca_software_publisher</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Construction Products Regulation data share</t>
+          <t>LCA software publisher</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Automatic</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
@@ -13611,22 +13554,22 @@
       <c r="A105" s="5" t="inlineStr"/>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>lca_data_ecodesign_share</t>
+          <t>lca_software_version</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Ecodesign and energy labelling data share</t>
+          <t>LCA software version</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>Automatic</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
@@ -13636,22 +13579,22 @@
       <c r="A106" s="5" t="inlineStr"/>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>lca_data_project_specific_share</t>
+          <t>lca_database_name</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Project-specific data share</t>
+          <t>LCA database name</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>Automatic</t>
+          <t>LCADatabase</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
@@ -13661,22 +13604,22 @@
       <c r="A107" s="5" t="inlineStr"/>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>lca_data_product_specific_share</t>
+          <t>lca_database_system_model</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Product-specific data share</t>
+          <t>Database system model</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Automatic</t>
+          <t>LCADatabaseSystemModel</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
@@ -13686,22 +13629,22 @@
       <c r="A108" s="5" t="inlineStr"/>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>lca_data_product_group_average_share</t>
+          <t>lca_database_version</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Average data for a product group share</t>
+          <t>LCA database version</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>Automatic</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
@@ -13711,12 +13654,12 @@
       <c r="A109" s="5" t="inlineStr"/>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>lca_data_generic_share</t>
+          <t>lca_data_cpr_share</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Generic data share</t>
+          <t>Construction Products Regulation data share</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -13736,12 +13679,12 @@
       <c r="A110" s="5" t="inlineStr"/>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>lca_data_default_share</t>
+          <t>lca_data_ecodesign_share</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Default values share</t>
+          <t>Ecodesign and energy labelling data share</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -13761,12 +13704,12 @@
       <c r="A111" s="5" t="inlineStr"/>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>lca_data_undeclared_share</t>
+          <t>lca_data_project_specific_share</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Undeclared share</t>
+          <t>Project-specific data share</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -13786,17 +13729,17 @@
       <c r="A112" s="5" t="inlineStr"/>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>lca_data_weighting_basis</t>
+          <t>lca_data_product_specific_share</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Data quality weighting basis</t>
+          <t>Product-specific data share</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>DataWeightingBasis</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -13811,12 +13754,12 @@
       <c r="A113" s="5" t="inlineStr"/>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>lca_completeness_score</t>
+          <t>lca_data_product_group_average_share</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Submission completeness</t>
+          <t>Average data for a product group share</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -13836,22 +13779,22 @@
       <c r="A114" s="5" t="inlineStr"/>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>lca_undeclared_material_note</t>
+          <t>lca_data_generic_share</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Undeclared material justification</t>
+          <t>Generic data share</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
@@ -13861,22 +13804,22 @@
       <c r="A115" s="5" t="inlineStr"/>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>lca_temporal_approach</t>
+          <t>lca_data_default_share</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>LCA temporal approach</t>
+          <t>Default values share</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>LCATemporalApproach</t>
-        </is>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
@@ -13886,22 +13829,22 @@
       <c r="A116" s="5" t="inlineStr"/>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>lca_onsite_renewable_allocation</t>
+          <t>lca_data_undeclared_share</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Allocation of embodied emissions of on-site renewable energy production</t>
+          <t>Undeclared share</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>OnSiteRenewableAllocationApproach</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
@@ -13911,22 +13854,22 @@
       <c r="A117" s="5" t="inlineStr"/>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>lca_shared_component_allocation_rule</t>
+          <t>lca_data_weighting_basis</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Rule for allocating emissions of shared building components</t>
+          <t>Data quality weighting basis</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>SharedComponentAllocationRule</t>
-        </is>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>DataWeightingBasis</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr"/>
@@ -13936,22 +13879,22 @@
       <c r="A118" s="5" t="inlineStr"/>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>lca_extended_default_data_use</t>
+          <t>lca_completeness_score</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Extended use of default data</t>
+          <t>Submission completeness</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
@@ -13961,22 +13904,22 @@
       <c r="A119" s="5" t="inlineStr"/>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>lca_extended_default_data_basis</t>
+          <t>lca_undeclared_material_note</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Basis for the extended use of default data</t>
+          <t>Undeclared material justification</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDefaultDataBasis</t>
-        </is>
-      </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr"/>
@@ -13986,17 +13929,17 @@
       <c r="A120" s="5" t="inlineStr"/>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>lca_limit_value_compliance</t>
+          <t>lca_temporal_approach</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Verification of compliance with a limit value</t>
+          <t>LCA temporal approach</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>LCATemporalApproach</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -14011,22 +13954,22 @@
       <c r="A121" s="5" t="inlineStr"/>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>lca_limit_value_scope_reduction</t>
+          <t>lca_onsite_renewable_allocation</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Parts left out for the verification of compliance</t>
+          <t>Allocation of embodied emissions of on-site renewable energy production</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>LimitValueScopeReduction</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>OnSiteRenewableAllocationApproach</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr"/>
@@ -14036,22 +13979,22 @@
       <c r="A122" s="5" t="inlineStr"/>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>lca_emission_factor_scenario</t>
+          <t>lca_shared_component_allocation_rule</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Emission factor scenario</t>
+          <t>Rule for allocating emissions of shared building components</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>EmissionFactorScenario</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+          <t>SharedComponentAllocationRule</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr"/>
@@ -14061,17 +14004,17 @@
       <c r="A123" s="5" t="inlineStr"/>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>lca_lci_modeling_approach</t>
+          <t>lca_extended_default_data_use</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>LCI modeling approach</t>
+          <t>Extended use of default data</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>LCIModelingApproach</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -14086,22 +14029,22 @@
       <c r="A124" s="5" t="inlineStr"/>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>lca_cycle_system_boundary</t>
+          <t>lca_extended_default_data_basis</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Life cycle system boundary</t>
+          <t>Basis for the extended use of default data</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>LifeCycleSystemBoundary</t>
-        </is>
-      </c>
-      <c r="E124" s="9" t="inlineStr">
-        <is>
-          <t>Required</t>
+          <t>ExtendedDefaultDataBasis</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr"/>
@@ -14111,22 +14054,22 @@
       <c r="A125" s="5" t="inlineStr"/>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>lcia_methodology</t>
+          <t>lca_limit_value_compliance</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>LCIA Methodology</t>
+          <t>Verification of compliance with a limit value</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>LCIAMethodology</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr"/>
@@ -14136,22 +14079,22 @@
       <c r="A126" s="5" t="inlineStr"/>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>lca_biogenic_method</t>
+          <t>lca_limit_value_scope_reduction</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Biogenic Carbon Accounting Method</t>
+          <t>Parts left out for the verification of compliance</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>BiogenicCarbonAccounting</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+          <t>LimitValueScopeReduction</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
@@ -14161,17 +14104,17 @@
       <c r="A127" s="5" t="inlineStr"/>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>lca_biogenic_carbon</t>
+          <t>lca_emission_factor_scenario</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Biogenic Carbon</t>
+          <t>Emission factor scenario</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>EmissionFactorScenario</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
@@ -14186,22 +14129,22 @@
       <c r="A128" s="5" t="inlineStr"/>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>lca_material_source</t>
+          <t>lca_lci_modeling_approach</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>LCA Material Quantities Source</t>
+          <t>LCI modeling approach</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>MaterialQuantitiesSource</t>
-        </is>
-      </c>
-      <c r="E128" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+          <t>LCIModelingApproach</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr"/>
@@ -14211,22 +14154,22 @@
       <c r="A129" s="5" t="inlineStr"/>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>lca_gwp_total_declared</t>
+          <t>lca_cycle_system_boundary</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total</t>
+          <t>Life cycle system boundary</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>Strongly recommended</t>
+          <t>LifeCycleSystemBoundary</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr"/>
@@ -14236,22 +14179,22 @@
       <c r="A130" s="5" t="inlineStr"/>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>lca_gwp_f_declared</t>
+          <t>lcia_methodology</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil</t>
+          <t>LCIA Methodology</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="E130" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+          <t>LCIAMethodology</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr"/>
@@ -14261,22 +14204,22 @@
       <c r="A131" s="5" t="inlineStr"/>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>lca_gwp_b_declared</t>
+          <t>lca_biogenic_method</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic</t>
+          <t>Biogenic Carbon Accounting Method</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="E131" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+          <t>BiogenicCarbonAccounting</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr"/>
@@ -14286,12 +14229,12 @@
       <c r="A132" s="5" t="inlineStr"/>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>lca_gwp_luc_declared</t>
+          <t>lca_biogenic_carbon</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change</t>
+          <t>Biogenic Carbon</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -14299,9 +14242,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E132" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr"/>
@@ -14311,22 +14254,22 @@
       <c r="A133" s="5" t="inlineStr"/>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>lca_odp_declared</t>
+          <t>lca_material_source</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential</t>
+          <t>LCA Material Quantities Source</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+          <t>MaterialQuantitiesSource</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr"/>
@@ -14336,12 +14279,12 @@
       <c r="A134" s="5" t="inlineStr"/>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>lca_ap_declared</t>
+          <t>lca_gwp_total_declared</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Acidification potential</t>
+          <t>Global Warming Potential - Total</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -14349,9 +14292,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E134" s="10" t="inlineStr">
-        <is>
-          <t>Suggested</t>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>Strongly recommended</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr"/>
@@ -14361,12 +14304,12 @@
       <c r="A135" s="5" t="inlineStr"/>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>lca_ap_ae_declared</t>
+          <t>lca_gwp_f_declared</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Acidification Potential - Accumulated Exceedance</t>
+          <t>Global Warming Potential - Fossil</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -14386,12 +14329,12 @@
       <c r="A136" s="5" t="inlineStr"/>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>lca_ep_declared</t>
+          <t>lca_gwp_b_declared</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Eutrophication Potential</t>
+          <t>Global Warming Potential - Biogenic</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -14411,12 +14354,12 @@
       <c r="A137" s="5" t="inlineStr"/>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>lca_ep_af_declared</t>
+          <t>lca_gwp_luc_declared</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater</t>
+          <t>Global Warming Potential - Land Use and Land Use Change</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -14436,12 +14379,12 @@
       <c r="A138" s="5" t="inlineStr"/>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>lca_ep_am_declared</t>
+          <t>lca_odp_declared</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine</t>
+          <t>Ozone Depletion Potential</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -14461,12 +14404,12 @@
       <c r="A139" s="5" t="inlineStr"/>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>lca_ep_t_declared</t>
+          <t>lca_ap_declared</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial</t>
+          <t>Acidification potential</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -14486,12 +14429,12 @@
       <c r="A140" s="5" t="inlineStr"/>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>lca_pocp_declared</t>
+          <t>lca_ap_ae_declared</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential</t>
+          <t>Acidification Potential - Accumulated Exceedance</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -14511,12 +14454,12 @@
       <c r="A141" s="5" t="inlineStr"/>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>lca_sfp_declared</t>
+          <t>lca_ep_declared</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Smog Forming Potential</t>
+          <t>Eutrophication Potential</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -14536,12 +14479,12 @@
       <c r="A142" s="5" t="inlineStr"/>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>lca_pofp_declared</t>
+          <t>lca_ep_af_declared</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential</t>
+          <t>Eutrophication Potential - Aquatic Freshwater</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -14561,12 +14504,12 @@
       <c r="A143" s="5" t="inlineStr"/>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>lca_adpmm_declared</t>
+          <t>lca_ep_am_declared</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals)</t>
+          <t>Eutrophication Potential - Aquatic Marine</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -14586,12 +14529,12 @@
       <c r="A144" s="5" t="inlineStr"/>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>lca_adpf_declared</t>
+          <t>lca_ep_t_declared</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels)</t>
+          <t>Eutrophication Potential - Terrestrial</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -14611,12 +14554,12 @@
       <c r="A145" s="5" t="inlineStr"/>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>lca_wdp_declared</t>
+          <t>lca_pocp_declared</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Water deprivation potential (deprivation-weighted water consumption)</t>
+          <t>Photochemical Ozone Creation Potential</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -14636,12 +14579,12 @@
       <c r="A146" s="5" t="inlineStr"/>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>lca_pere_declared</t>
+          <t>lca_sfp_declared</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources)</t>
+          <t>Smog Forming Potential</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -14661,12 +14604,12 @@
       <c r="A147" s="5" t="inlineStr"/>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>lca_penre_declared</t>
+          <t>lca_pofp_declared</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources)</t>
+          <t>Photochemical Ozone Formation Potential</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -14686,12 +14629,12 @@
       <c r="A148" s="5" t="inlineStr"/>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>lca_pert_declared</t>
+          <t>lca_adpmm_declared</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals)</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -14711,12 +14654,12 @@
       <c r="A149" s="5" t="inlineStr"/>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>lca_penrt_declared</t>
+          <t>lca_adpf_declared</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels)</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -14736,12 +14679,12 @@
       <c r="A150" s="5" t="inlineStr"/>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>lca_pm_declared</t>
+          <t>lca_wdp_declared</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Particulate Matter Emissions</t>
+          <t>Water deprivation potential (deprivation-weighted water consumption)</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -14749,9 +14692,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E150" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr"/>
@@ -14761,12 +14704,12 @@
       <c r="A151" s="5" t="inlineStr"/>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>lca_irp_declared</t>
+          <t>lca_pere_declared</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Ionising Radiation - Human Health</t>
+          <t>Primary Energy Renewable (Energy resources)</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -14774,9 +14717,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr"/>
@@ -14786,12 +14729,12 @@
       <c r="A152" s="5" t="inlineStr"/>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>lca_etp_fw_declared</t>
+          <t>lca_penre_declared</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Ecotoxicity - Freshwater</t>
+          <t>Primary Energy Non-Renewable (Energy resources)</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -14799,9 +14742,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr"/>
@@ -14811,12 +14754,12 @@
       <c r="A153" s="5" t="inlineStr"/>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>lca_htp_c_declared</t>
+          <t>lca_pert_declared</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Human Toxicity - Cancer Effects</t>
+          <t>Primary Energy Renewable Total</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -14824,9 +14767,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr"/>
@@ -14836,12 +14779,12 @@
       <c r="A154" s="5" t="inlineStr"/>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>lca_htp_nc_declared</t>
+          <t>lca_penrt_declared</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Human Toxicity - Non-cancer Effects</t>
+          <t>Primary Energy Non-Renewable Total</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -14849,9 +14792,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr"/>
@@ -14861,12 +14804,12 @@
       <c r="A155" s="5" t="inlineStr"/>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>lca_sqp_declared</t>
+          <t>lca_pm_declared</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Soil Quality Index</t>
+          <t>Particulate Matter Emissions</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -14886,12 +14829,12 @@
       <c r="A156" s="5" t="inlineStr"/>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>lca_a1_3</t>
+          <t>lca_irp_declared</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>A1-A3: Product Stage</t>
+          <t>Ionising Radiation - Human Health</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -14899,9 +14842,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr"/>
@@ -14911,12 +14854,12 @@
       <c r="A157" s="5" t="inlineStr"/>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>lca_a1</t>
+          <t>lca_etp_fw_declared</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>A1 Raw Material Supply</t>
+          <t>Ecotoxicity - Freshwater</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -14924,9 +14867,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E157" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr"/>
@@ -14936,12 +14879,12 @@
       <c r="A158" s="5" t="inlineStr"/>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>lca_a2</t>
+          <t>lca_htp_c_declared</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>A2 Transport</t>
+          <t>Human Toxicity - Cancer Effects</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -14949,9 +14892,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E158" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr"/>
@@ -14961,12 +14904,12 @@
       <c r="A159" s="5" t="inlineStr"/>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>lca_a3</t>
+          <t>lca_htp_nc_declared</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>A3 Manufacturing</t>
+          <t>Human Toxicity - Non-cancer Effects</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -14974,9 +14917,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E159" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr"/>
@@ -14986,12 +14929,12 @@
       <c r="A160" s="5" t="inlineStr"/>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>lca_a4</t>
+          <t>lca_sqp_declared</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>A4 Transport</t>
+          <t>Soil Quality Index</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -14999,9 +14942,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E160" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr"/>
@@ -15011,12 +14954,12 @@
       <c r="A161" s="5" t="inlineStr"/>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>lca_a5</t>
+          <t>lca_a1_3</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>A5 Construction/Installation: Installation of the product into the building</t>
+          <t>A1-A3: Product Stage</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -15036,12 +14979,12 @@
       <c r="A162" s="5" t="inlineStr"/>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>lca_a5_1</t>
+          <t>lca_a1</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>A5.1 Pre-construction demolition</t>
+          <t>A1 Raw Material Supply</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -15049,9 +14992,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E162" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr"/>
@@ -15061,12 +15004,12 @@
       <c r="A163" s="5" t="inlineStr"/>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>lca_a5_2</t>
+          <t>lca_a2</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>A5.2 Construction activities</t>
+          <t>A2 Transport</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -15074,9 +15017,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E163" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr"/>
@@ -15086,12 +15029,12 @@
       <c r="A164" s="5" t="inlineStr"/>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>lca_a5_3</t>
+          <t>lca_a3</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>A5.3 Waste and waste management</t>
+          <t>A3 Manufacturing</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -15099,9 +15042,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E164" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr"/>
@@ -15111,12 +15054,12 @@
       <c r="A165" s="5" t="inlineStr"/>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>lca_a5_4</t>
+          <t>lca_a4</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>A5.4 Worker transport</t>
+          <t>A4 Transport</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -15124,9 +15067,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E165" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr"/>
@@ -15136,12 +15079,12 @@
       <c r="A166" s="5" t="inlineStr"/>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>lca_b1</t>
+          <t>lca_a5</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>B1 Use: Environmental impacts arising from the product in use (eg, release of substances)</t>
+          <t>A5 Construction/Installation: Installation of the product into the building</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -15161,12 +15104,12 @@
       <c r="A167" s="5" t="inlineStr"/>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>lca_b1_1</t>
+          <t>lca_a5_1</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>B1.1 Emissions from materials and carbonation</t>
+          <t>A5.1 Pre-construction demolition</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -15186,12 +15129,12 @@
       <c r="A168" s="5" t="inlineStr"/>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>lca_b1_2</t>
+          <t>lca_a5_2</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>B1.2 Fugitive emissions of refrigerants</t>
+          <t>A5.2 Construction activities</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -15211,12 +15154,12 @@
       <c r="A169" s="5" t="inlineStr"/>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>lca_b2</t>
+          <t>lca_a5_3</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>B2 Maintenance: Actions to maintain the product's functional quality (cleaning, painting)</t>
+          <t>A5.3 Waste and waste management</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -15224,9 +15167,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E169" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr"/>
@@ -15236,12 +15179,12 @@
       <c r="A170" s="5" t="inlineStr"/>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>lca_b3</t>
+          <t>lca_a5_4</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>B3 Repair: Corrective actions to return the product to a functional state</t>
+          <t>A5.4 Worker transport</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -15249,9 +15192,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E170" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr"/>
@@ -15261,12 +15204,12 @@
       <c r="A171" s="5" t="inlineStr"/>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>lca_b4</t>
+          <t>lca_b1</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>B4 Replacement: Replacing the product or parts of it at the end of its service life</t>
+          <t>B1 Use: Environmental impacts arising from the product in use (eg, release of substances)</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -15286,12 +15229,12 @@
       <c r="A172" s="5" t="inlineStr"/>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>lca_b5</t>
+          <t>lca_b1_1</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>B5 Refurbishment: Major changes to restore or improve performance</t>
+          <t>B1.1 Emissions from materials and carbonation</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -15299,9 +15242,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E172" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr"/>
@@ -15311,12 +15254,12 @@
       <c r="A173" s="5" t="inlineStr"/>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>lca_b6</t>
+          <t>lca_b1_2</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>B6 Operational Energy Use: Energy consumption related to the building's operation (heating, cooling, lighting)</t>
+          <t>B1.2 Fugitive emissions of refrigerants</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -15324,9 +15267,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E173" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr"/>
@@ -15336,12 +15279,12 @@
       <c r="A174" s="5" t="inlineStr"/>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>lca_b6_1</t>
+          <t>lca_b2</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>B6.1 Regulated building-integrated systems</t>
+          <t>B2 Maintenance: Actions to maintain the product's functional quality (cleaning, painting)</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -15349,9 +15292,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr"/>
@@ -15361,12 +15304,12 @@
       <c r="A175" s="5" t="inlineStr"/>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>lca_b6_2</t>
+          <t>lca_b3</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>B6.2 Non-regulated building-integrated systems</t>
+          <t>B3 Repair: Corrective actions to return the product to a functional state</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -15374,9 +15317,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr"/>
@@ -15386,12 +15329,12 @@
       <c r="A176" s="5" t="inlineStr"/>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>lca_b6_3</t>
+          <t>lca_b4</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>B6.3 Other energy use related to user activities</t>
+          <t>B4 Replacement: Replacing the product or parts of it at the end of its service life</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -15399,9 +15342,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E176" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr"/>
@@ -15411,12 +15354,12 @@
       <c r="A177" s="5" t="inlineStr"/>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>lca_b7</t>
+          <t>lca_b5</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>B7 Operational Water Use: Water consumption related to the building's operation</t>
+          <t>B5 Refurbishment: Major changes to restore or improve performance</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -15436,12 +15379,12 @@
       <c r="A178" s="5" t="inlineStr"/>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>lca_b7_1</t>
+          <t>lca_b6</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>B7.1 Essential building-integrated systems</t>
+          <t>B6 Operational Energy Use: Energy consumption related to the building's operation (heating, cooling, lighting)</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -15449,9 +15392,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E178" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr"/>
@@ -15461,12 +15404,12 @@
       <c r="A179" s="5" t="inlineStr"/>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>lca_b7_2</t>
+          <t>lca_b6_1</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>B7.2 Other building-integrated systems</t>
+          <t>B6.1 Regulated building-integrated systems</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -15486,12 +15429,12 @@
       <c r="A180" s="5" t="inlineStr"/>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>lca_b7_3</t>
+          <t>lca_b6_2</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>B7.3 Non-building-integrated systems</t>
+          <t>B6.2 Non-regulated building-integrated systems</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -15511,12 +15454,12 @@
       <c r="A181" s="5" t="inlineStr"/>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>lca_b8</t>
+          <t>lca_b6_3</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>B8 Building-integrated users activities</t>
+          <t>B6.3 Other energy use related to user activities</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -15536,12 +15479,12 @@
       <c r="A182" s="5" t="inlineStr"/>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>lca_b8_1</t>
+          <t>lca_b7</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>B8.1 Transport of persons</t>
+          <t>B7 Operational Water Use: Water consumption related to the building's operation</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -15549,9 +15492,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E182" s="8" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E182" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr"/>
@@ -15561,12 +15504,12 @@
       <c r="A183" s="5" t="inlineStr"/>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>lca_b8_2</t>
+          <t>lca_b7_1</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>B8.2 Charging of electric vehicles</t>
+          <t>B7.1 Essential building-integrated systems</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -15586,12 +15529,12 @@
       <c r="A184" s="5" t="inlineStr"/>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>lca_b8_3</t>
+          <t>lca_b7_2</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>B8.3 Other user activities</t>
+          <t>B7.2 Other building-integrated systems</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -15611,12 +15554,12 @@
       <c r="A185" s="5" t="inlineStr"/>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>lca_c1</t>
+          <t>lca_b7_3</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>C1 De-construction/Demolition: Dismantling or demolishing the building/product</t>
+          <t>B7.3 Non-building-integrated systems</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -15624,9 +15567,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E185" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E185" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr"/>
@@ -15636,12 +15579,12 @@
       <c r="A186" s="5" t="inlineStr"/>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>lca_c2</t>
+          <t>lca_b8</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>C2 Transport: Transporting the waste to processing or disposal sites</t>
+          <t>B8 Building-integrated users activities</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -15649,9 +15592,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E186" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E186" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr"/>
@@ -15661,12 +15604,12 @@
       <c r="A187" s="5" t="inlineStr"/>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>lca_c3</t>
+          <t>lca_b8_1</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>C3 Waste Processing: Processing waste for reuse, recovery, or recycling</t>
+          <t>B8.1 Transport of persons</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -15674,9 +15617,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E187" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E187" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr"/>
@@ -15686,12 +15629,12 @@
       <c r="A188" s="5" t="inlineStr"/>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>lca_c4</t>
+          <t>lca_b8_2</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>C4 Disposal: Final disposal of waste that cannot be recovered (eg, landfill)</t>
+          <t>B8.2 Charging of electric vehicles</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -15699,9 +15642,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E188" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr"/>
@@ -15711,12 +15654,12 @@
       <c r="A189" s="5" t="inlineStr"/>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>lca_d</t>
+          <t>lca_b8_3</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>D Benefits and Loads Beyond the System Boundary</t>
+          <t>B8.3 Other user activities</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -15724,9 +15667,9 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="E189" s="12" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr"/>
@@ -15736,12 +15679,12 @@
       <c r="A190" s="5" t="inlineStr"/>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>lca_d1</t>
+          <t>lca_c1</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>D1 Reuse, Recovery, and Recycling Potential: Net benefits or loads resulting from reusing or recycling materials (avoided emissions)</t>
+          <t>C1 De-construction/Demolition: Dismantling or demolishing the building/product</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -15761,12 +15704,12 @@
       <c r="A191" s="5" t="inlineStr"/>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>lca_d2</t>
+          <t>lca_c2</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>D2 Exported Energy (or Energy Recovery Potential)</t>
+          <t>C2 Transport: Transporting the waste to processing or disposal sites</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -15781,6 +15724,131 @@
       </c>
       <c r="F191" s="5" t="inlineStr"/>
       <c r="G191" s="5" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr"/>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>lca_c3</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>C3 Waste Processing: Processing waste for reuse, recovery, or recycling</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E192" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr"/>
+      <c r="G192" s="5" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr"/>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>lca_c4</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>C4 Disposal: Final disposal of waste that cannot be recovered (eg, landfill)</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E193" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr"/>
+      <c r="G193" s="5" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr"/>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>lca_d</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>D Benefits and Loads Beyond the System Boundary</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E194" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr"/>
+      <c r="G194" s="5" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr"/>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>lca_d1</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>D1 Reuse, Recovery, and Recycling Potential: Net benefits or loads resulting from reusing or recycling materials (avoided emissions)</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr"/>
+      <c r="G195" s="5" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr"/>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>lca_d2</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>D2 Exported Energy (or Energy Recovery Potential)</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E196" s="12" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr"/>
+      <c r="G196" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15788,6 +15856,298 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="140" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Value in your format</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF enum value</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value display name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value description (if any)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value parent category (if applicable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>OKOBAUDAT_20.23.050</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>OKOBAUDAT_20.23.050</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>OKOBAUDAT_20.24.070</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>OKOBAUDAT_20.24.070</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>habitat2030_BIGTEN</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>habitat2030_BIGTEN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>IBU_Data</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>IBU_Data</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>EC3</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>EC3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>ecoinvent</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Ecoinvent</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="140" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Value in your format</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF enum value</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value display name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value description (if any)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value parent category (if applicable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>cut_off</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Cut off (recycled content approach, ecoinvent cut-off)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>recycled content approach, ecoinvent cut-off</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>cut_off_en15804</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Cut off EN15804 (ecoinvent system model aligned with EN 15804)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ecoinvent system model aligned with EN 15804</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>apos</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>APOS (allocation at the point of substitution)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>allocation at the point of substitution</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>consequential</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Consequential (marginal, market-driven modelling)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>marginal, market-driven modelling</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15834,17 +16194,17 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>gwp_fossil_a1_a3</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Integer (whole replacements only)</t>
+          <t>GWP fossil a1 a3 (shares weighted by fossil global warming potential of modules A1 to A3)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>whole replacements only</t>
+          <t>shares weighted by fossil global warming potential of modules A1 to A3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -15853,17 +16213,17 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>mass</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Decimal (fractional replacements allowed)</t>
+          <t>Mass (shares weighted by mass)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>fractional replacements allowed</t>
+          <t>shares weighted by mass</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -15872,17 +16232,17 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_computed</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Unknown (rule not declared)</t>
+          <t>Not computed (shares not weighted)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rule not declared</t>
+          <t>shares not weighted</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -15892,13 +16252,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15939,12 +16299,12 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>OKOBAUDAT_20.23.050</t>
+          <t>static</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>OKOBAUDAT_20.23.050</t>
+          <t>Static (impacts not distributed over time)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -15954,12 +16314,12 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>OKOBAUDAT_20.24.070</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>OKOBAUDAT_20.24.070</t>
+          <t>Dynamic (impacts distributed over time)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -15969,12 +16329,12 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>habitat2030_BIGTEN</t>
+          <t>probabilistic</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>habitat2030_BIGTEN</t>
+          <t>Probabilistic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -15984,68 +16344,128 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>IBU_Data</t>
+          <t>prospective</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>IBU_Data</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>EC3</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>EC3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>ecoinvent</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Ecoinvent</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="140" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Value in your format</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF enum value</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value display name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value description (if any)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value parent category (if applicable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>approach_a</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>approach_a (full allocation to the building of energy storage components and of all other system parts)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>full allocation to the building of energy storage components and of all other system parts</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>approach_b1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>approach_b1 (full allocation of energy storage components; other system parts allocated in proportion to the share of captured or generated energy used for self-consumption)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>full allocation of energy storage components; other system parts allocated in proportion to the share of captured or generated energy used for self-consumption</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>approach_b2</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>approach_b2 (full allocation of energy storage components; components integrated into the building envelope and forming its surface allocated in full, with the remaining embodied emissions allocated in proportion to the share used for self-consumption)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>full allocation of energy storage components; components integrated into the building envelope and forming its surface allocated in full, with the remaining embodied emissions allocated in proportion to the share used for self-consumption</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16092,17 +16512,17 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>cut_off</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Cut off (recycled content approach, ecoinvent cut-off)</t>
+          <t>not_applicable (the submission covers a single building)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>recycled content approach, ecoinvent cut-off</t>
+          <t>the submission covers a single building</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -16111,17 +16531,17 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>cut_off_en15804</t>
+          <t>single_assessment</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Cut off EN15804 (ecoinvent system model aligned with EN 15804)</t>
+          <t>single_assessment (the whole complex of buildings constitutes one single assessment)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ecoinvent system model aligned with EN 15804</t>
+          <t>the whole complex of buildings constitutes one single assessment</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -16130,17 +16550,17 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>apos</t>
+          <t>building_units</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>APOS (allocation at the point of substitution)</t>
+          <t>building_units (the total is divided proportionately between the owner building units)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>allocation at the point of substitution</t>
+          <t>the total is divided proportionately between the owner building units</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -16149,17 +16569,17 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>consequential</t>
+          <t>parking_spaces</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Consequential (marginal, market-driven modelling)</t>
+          <t>parking_spaces (allocated on the basis of the relative shares of parking spaces designated to each building)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>marginal, market-driven modelling</t>
+          <t>allocated on the basis of the relative shares of parking spaces designated to each building</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -16168,15 +16588,19 @@
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>other (a national rule, stated in the assessor note)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>a national rule, stated in the assessor note</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -16184,112 +16608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="140" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Value in your format</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF enum value</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value display name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value description (if any)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value parent category (if applicable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>gwp_fossil_a1_a3</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>GWP fossil a1 a3 (shares weighted by fossil global warming potential of modules A1 to A3)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>shares weighted by fossil global warming potential of modules A1 to A3</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>mass</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Mass (shares weighted by mass)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>shares weighted by mass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>not_computed</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Not computed (shares not weighted)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>shares not weighted</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16336,309 +16655,77 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>outermost_region</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Static (impacts not distributed over time)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Outermost region</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>an outermost region within the meaning of Article 349 TFEU</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>dynamic</t>
+          <t>data_gap</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Dynamic (impacts distributed over time)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Data gap (default values used to fill data gaps where no other type of data is available)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>default values used to fill data gaps where no other type of data is available</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>probabilistic</t>
+          <t>simplified_calculation</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Probabilistic</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Simplified Calculation (default values used where it is necessary to simplify the calculation)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>default values used where it is necessary to simplify the calculation</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>prospective</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Prospective</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Other (stated in the assessor note)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>stated in the assessor note</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="140" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Value in your format</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF enum value</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value display name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value description (if any)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value parent category (if applicable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>approach_a</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>approach_a (full allocation to the building of energy storage components and of all other system parts)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>full allocation to the building of energy storage components and of all other system parts</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>approach_b1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>approach_b1 (full allocation of energy storage components; other system parts allocated in proportion to the share of captured or generated energy used for self-consumption)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>full allocation of energy storage components; other system parts allocated in proportion to the share of captured or generated energy used for self-consumption</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>approach_b2</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>approach_b2 (full allocation of energy storage components; components integrated into the building envelope and forming its surface allocated in full, with the remaining embodied emissions allocated in proportion to the share used for self-consumption)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>full allocation of energy storage components; components integrated into the building envelope and forming its surface allocated in full, with the remaining embodied emissions allocated in proportion to the share used for self-consumption</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="140" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Value in your format</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF enum value</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value display name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value description (if any)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value parent category (if applicable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>not_applicable (the submission covers a single building)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>the submission covers a single building</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>single_assessment</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>single_assessment (the whole complex of buildings constitutes one single assessment)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>the whole complex of buildings constitutes one single assessment</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>building_units</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>building_units (the total is divided proportionately between the owner building units)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>the total is divided proportionately between the owner building units</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>parking_spaces</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>parking_spaces (allocated on the basis of the relative shares of parking spaces designated to each building)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>allocated on the basis of the relative shares of parking spaces designated to each building</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>other (a national rule, stated in the assessor note)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>a national rule, stated in the assessor note</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16692,17 +16779,17 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>outermost_region</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Outermost region</t>
+          <t>None (nothing left out, the result is a complete assessment)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>an outermost region within the meaning of Article 349 TFEU</t>
+          <t>nothing left out, the result is a complete assessment</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -16711,17 +16798,17 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>data_gap</t>
+          <t>life_cycle_stages</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Data gap (default values used to fill data gaps where no other type of data is available)</t>
+          <t>Life cycle stages</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>default values used to fill data gaps where no other type of data is available</t>
+          <t>parts of life-cycle stages left out</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -16730,17 +16817,17 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>simplified_calculation</t>
+          <t>scope_of_building_components</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Simplified Calculation (default values used where it is necessary to simplify the calculation)</t>
+          <t>Scope of building components</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>default values used where it is necessary to simplify the calculation</t>
+          <t>parts of the scope of building components left out</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -16749,17 +16836,17 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Other (stated in the assessor note)</t>
+          <t>Both (parts of life-cycle stages and parts of the scope of building components left out)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>stated in the assessor note</t>
+          <t>parts of life-cycle stages and parts of the scope of building components left out</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -16770,6 +16857,111 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="140" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Value in your format</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF enum value</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value display name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value description (if any)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value parent category (if applicable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable (no operational energy calculated)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>no operational energy calculated</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>None (no forward-looking factors; the factors of the base Year apply over the whole period)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>no forward-looking factors; the factors of the base year apply over the whole period</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>forward_looking</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>forward_looking (forward-looking emission factors, justified, consistent and clearly defined for the whole reference study period)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>forward-looking emission factors, justified, consistent and clearly defined for the whole reference study period</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16816,17 +17008,17 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>process_based</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>None (nothing left out, the result is a complete assessment)</t>
+          <t>Process-based (Typically bottom-up, highly specific data)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nothing left out, the result is a complete assessment</t>
+          <t>Calculates impacts by summing individual process steps.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -16835,17 +17027,17 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>life_cycle_stages</t>
+          <t>io_based</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Life cycle stages</t>
+          <t>Environmentally Extended Input-Output (EEIO) (Top-down, based on economic sector averages)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>parts of life-cycle stages left out</t>
+          <t>Input-Output based modeling using economic data.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -16854,17 +17046,17 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>scope_of_building_components</t>
+          <t>hybrid_based</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Scope of building components</t>
+          <t>Hybrid (A mix of process data and IO data)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>parts of the scope of building components left out</t>
+          <t>Combines both process-based and I-O based methodologies.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -16873,125 +17065,20 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Both (parts of life-cycle stages and parts of the scope of building components left out)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>parts of life-cycle stages and parts of the scope of building components left out</t>
+          <t>Alternative LCA modeling methodology.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="140" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Value in your format</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF enum value</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value display name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value description (if any)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value parent category (if applicable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Not applicable (no operational energy calculated)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>no operational energy calculated</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>None (no forward-looking factors; the factors of the base Year apply over the whole period)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>no forward-looking factors; the factors of the base year apply over the whole period</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>forward_looking</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>forward_looking (forward-looking emission factors, justified, consistent and clearly defined for the whole reference study period)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>forward-looking emission factors, justified, consistent and clearly defined for the whole reference study period</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17764,130 +17851,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="140" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Value in your format</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF enum value</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value display name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value description (if any)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value parent category (if applicable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>process_based</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Process-based (Typically bottom-up, highly specific data)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Calculates impacts by summing individual process steps.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>io_based</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Environmentally Extended Input-Output (EEIO) (Top-down, based on economic sector averages)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Input-Output based modeling using economic data.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>hybrid_based</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Hybrid (A mix of process data and IO data)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Combines both process-based and I-O based methodologies.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Alternative LCA modeling methodology.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18034,6 +17997,129 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="140" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Value in your format</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF enum value</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value display name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value description (if any)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value parent category (if applicable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>EN 15804:2012+A1:2013</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>EN 15804:2012+A1:2013</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>EN 15804:2012+A2:2019</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>EN 15804:2012+A2:2019</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>EN 15978:2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>EN 15978:2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>US EPA TRACI 2.1</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>US EPA TRACI 2.1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18087,42 +18173,50 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>EN 15804:2012+A1:2013</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>EN 15804:2012+A1:2013</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>0/0 (biogenic carbon not counted)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Neutral accounting (no sequestration/no emission)</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>EN 15804:2012+A2:2019</t>
+          <t>-1/+1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>EN 15804:2012+A2:2019</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>-1/+1 (uptake counted as negative and release as positive)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Credit at start / burden at end of life</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>EN 15978:2026</t>
+          <t>dynamic_lca</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>EN 15978:2026</t>
+          <t>Dynamic LCA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -18132,12 +18226,12 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>US EPA TRACI 2.1</t>
+          <t>ton_year</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>US EPA TRACI 2.1</t>
+          <t>Ton-Year Accounting or Discounting Method</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -18147,7 +18241,7 @@
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -18164,137 +18258,6 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="140" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Value in your format</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF enum value</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value display name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value description (if any)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value parent category (if applicable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>0/0 (biogenic carbon not counted)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Neutral accounting (no sequestration/no emission)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>-1/+1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>-1/+1 (uptake counted as negative and release as positive)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Credit at start / burden at end of life</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>dynamic_lca</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Dynamic LCA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>ton_year</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Ton-Year Accounting or Discounting Method</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18447,7 +18410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18525,7 +18488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22229,7 +22192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22575,6 +22538,187 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="140" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Value in your format</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF enum value</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value display name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value description (if any)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>OpenBDF value parent category (if applicable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>cpr_dopc</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Cpr dopc (declaration of performance and conformity under the Construction Products Regulation)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>declaration of performance and conformity under the Construction Products Regulation</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>ecodesign</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Ecodesign (data issued under ecodesign or energy labelling legislation)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data issued under ecodesign or energy labelling legislation</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>project_specific</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Project specific (assessment of this project, not issued under those rules)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>assessment of this project, not issued under those rules</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>product_specific</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Product specific (assessment of this product, not issued under those rules)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>assessment of this product, not issued under those rules</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>product_group_average</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Product group average (sectoral or industry average)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sectoral or industry average</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Generic (background database value)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>background database value</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>default_value</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Default value (conservative national default)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>conservative national default</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22628,17 +22772,17 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>cpr_dopc</t>
+          <t>identical</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Cpr dopc (declaration of performance and conformity under the Construction Products Regulation)</t>
+          <t>Identical (the declaration describes this product)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>declaration of performance and conformity under the Construction Products Regulation</t>
+          <t>the declaration describes this product</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -22647,17 +22791,17 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>ecodesign</t>
+          <t>same_product_group</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Ecodesign (data issued under ecodesign or energy labelling legislation)</t>
+          <t>Same product group (a sectoral average covering it)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data issued under ecodesign or energy labelling legislation</t>
+          <t>a sectoral average covering it</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -22666,17 +22810,17 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>project_specific</t>
+          <t>proxy_technological</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Project specific (assessment of this project, not issued under those rules)</t>
+          <t>Proxy technological (a different product used as a stand-in)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>assessment of this project, not issued under those rules</t>
+          <t>a different product used as a stand-in</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -22685,17 +22829,17 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>product_specific</t>
+          <t>proxy_geographical</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Product specific (assessment of this product, not issued under those rules)</t>
+          <t>Proxy geographical (the same product, another region)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>assessment of this product, not issued under those rules</t>
+          <t>the same product, another region</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -22704,17 +22848,17 @@
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>product_group_average</t>
+          <t>proxy_temporal</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Product group average (sectoral or industry average)</t>
+          <t>Proxy temporal (the same product, outside the validity of its declaration)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sectoral or industry average</t>
+          <t>the same product, outside the validity of its declaration</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -22723,17 +22867,17 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>reference_only</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Generic (background database value)</t>
+          <t>Reference only (a broad reference, not a match)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>background database value</t>
+          <t>a broad reference, not a match</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -22742,17 +22886,17 @@
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>default_value</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Default value (conservative national default)</t>
+          <t>Unknown (the relationship cannot be established)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>conservative national default</t>
+          <t>the relationship cannot be established</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -22809,133 +22953,105 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Identical (the declaration describes this product)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>the declaration describes this product</t>
-        </is>
-      </c>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>same_product_group</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Same product group (a sectoral average covering it)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>a sectoral average covering it</t>
-        </is>
-      </c>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>proxy_technological</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Proxy technological (a different product used as a stand-in)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>a different product used as a stand-in</t>
-        </is>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>proxy_geographical</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Proxy geographical (the same product, another region)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>the same product, another region</t>
-        </is>
-      </c>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>proxy_temporal</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Proxy temporal (the same product, outside the validity of its declaration)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>the same product, outside the validity of its declaration</t>
-        </is>
-      </c>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>reference_only</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Reference only (a broad reference, not a match)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>a broad reference, not a match</t>
-        </is>
-      </c>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Unknown (the relationship cannot be established)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>the relationship cannot be established</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
@@ -23584,159 +23700,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="140" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Value in your format</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF enum value</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value display name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value description (if any)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF value parent category (if applicable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>piece</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>piece</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
